--- a/regulatory-compliance/cloud-foundation/9.1/nist-800-207/vcf-91-companion-nist-800-207.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/nist-800-207/vcf-91-companion-nist-800-207.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -732,11 +747,10 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Services Platform (SSP) maintains an inventory of network-visible workloads organized into a hierarchical asset collection spanning regions, zones, environments, applications, and application tiers. The Publish Inventory Assets tab in SSP displays infrastructure asset details including asset names, asset types, IP addresses, and total VM counts for assets sourced from imported CSV files, discovered services, or published infrastructure assets, providing accurate, granular records of network-visible assets.
-Platform Inventory monitoring supports ongoing inventory accuracy through several mechanisms. Administrators can filter infrastructure assets by Name and Status, identifying assets that are timed out or out of sync. The inventory hierarchy view shows regions, zones, and VMs so administrators can verify correct definition. SSP Inventory displays assigned tags for each infrastructure asset, and environment rows can be expanded to view tag assignments and confirm hierarchy accuracy. The platform also collects and displays VM tags with their respective scopes, supporting classification and tracking. Published applications and their application types are verifiable in the Inventory &gt; Applications interface.
-SSP identifies and publishes application assets, classifying them as either critical or regular applications. Application Asset Collections represent groups of workloads delivering enterprise software functions. Security Intelligence within SSP displays application associations for compute entities, indicating the tiers within each application to which a given compute entity belongs. Administering compute entity classifications in Security Intelligence requires appropriate privileges, supporting access control over classification changes. Consistent naming conventions are recommended when preparing inventory data for import, and the Asset Prefix setting enables standardized naming during segmentation planning and monitoring.
-In disconnected mode, usage files include an asset_id field providing a unique asset identifier, supporting asset tracking in environments without continuous connectivity.
-vDefend's inventory scope is limited to network-visible workloads and does not replace enterprise-wide TAASD inventory tools, authorized software catalogs with business justification records, or data asset registries required for full AST-02 compliance.</t>
+          <t>VMware vDefend (DFW) and Gateway Firewall (GFW) can enforce network-level access controls that restrict which systems are able to communicate with internal resources. By applying policy rules based on workload identity and group membership, administrators can limit data flows to approved assets and block unauthorized endpoints from reaching internal services. The GFW supports enforcement of isolation between projects, allowing enterprise administrators to deny all inter-project communication except for essential infrastructure protocols such as DHCP, DNS, NTP, and ICMP, providing a boundary that limits which systems can reach internal resources.
+Security Services Platform's Platform Inventory provides the visibility needed to support these restrictions. Administrators can filter monitored assets by Name and Status to identify infrastructure assets and their operational state. The inventory identifies assets that are timed out or out of sync, providing early indication when a system's status may no longer match its approved configuration. Platform Inventory organizes assets into Regions and Zones with a hierarchical structure and displays assigned tags for each infrastructure asset, supporting verification of tag assignments.
+Security Intelligence's asset collections include groups, infrastructure assets, environments, applications, and application tiers. The Asset Collections view includes nodes representing entities that communicated with members of defined groups but are not part of the NSX inventory, giving administrators visibility into systems interacting with internal resources that fall outside the known asset baseline. This capability helps identify potential non-organizationally owned systems that are communicating with internal workloads. Security Intelligence Workload Classification allows administrators to mark compute entities as 'Others (Non-infrastructure)' to indicate that an entity does not provide infrastructure services, supporting identification of non-standard workloads. Security Services Platform also identifies and publishes application assets, classifying them as critical or regular, to support targeted policy application.
+These capabilities provide the network enforcement and asset visibility mechanisms that help administrators identify and restrict access by non-organizationally owned systems. vDefend does not manage procurement, asset authorization, or cataloging decisions; those remain organizational governance processes outside the product's scope.</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
@@ -813,29 +827,25 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>VCF implements cryptographic protections across its component stack using publicly standardized, validated cryptographic modules and algorithms.
-Multiple VCF components rely on cryptographic modules validated through the NIST Cryptographic Module Validation Program (CMVP) to FIPS 140-2 and FIPS 140-3 standards. NSX is configured to use FIPS 140-3 validated cryptographic modules by default, and NSX Manager uses FIPS 140 approved algorithms for authentication to its cryptographic module. Specific NSX validated modules include IKE with Rambus Safezone 2.0 (Certificate #4898), VMware OpenSSL 3.0.9 (Certificate #4861), VMware BouncyCastle 2.0.0 (Certificate #4986), and VMware BoringCrypto 6.0 (Certificate #4694). VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module, which holds FIPS 140-3 Certificate #4743. VCF Operations for Networks uses BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 with FIPS 140-2 Certificate #37009 as its validated cryptographic module. This consistent use of FIPS-validated modules across the platform means that organizations deploying VCF in regulated environments can rely on cryptographic implementations that have undergone independent validation against well-known public standards. The VMware Kubernetes Service (VKS) consumption layer also supports FIPS mode: VKS ClusterClass configurations include a fips.enabled variable that, when set, restricts cryptographic operations on cluster nodes to approved algorithm implementations. FIPS-enabled Kubernetes release images, identified by a -fips suffix in the release reference name, are available for organizations that require FIPS-validated cryptography across their containerized workloads.
-At the protocol and algorithm level, VCF enforces modern cryptographic standards throughout. Starting in vSphere 9.0, all TLS profiles are FIPS compliant; the COMPATIBLE profile supports modern TLS cipher suites with standardized elliptic curves. Monitoring infrastructure such as Telegraf enforces a modern TLS minimum version for secure communication. The NSX L2 VPN FIPS compliance suite uses AES-GCM encryption with Perfect Forward Secrecy and Diffie-Hellman Group 20. NSX also supports ECDSA (Elliptic Curve Digital Signature Algorithm) encryption for environments with high-assurance cryptographic requirements. VCF Operations for Networks supports several encryption algorithms and ciphers for its data sources. VCF Operations provides a FIPS Security Mode that, when enabled, applies additional algorithm and cipher prerequisites across the management domain. All system management network communications are encrypted by default using standardized cipher suites. At the VKS layer, Kubernetes control plane components expose parameters for restricting permitted TLS configurations: the kube-apiserver --tls-cipher-suites parameter, the kubelet tlsCipherSuites configuration field, and the equivalent parameter on the kube-scheduler each restrict the set of permitted cipher suites, allowing administrators to exclude deprecated or weak algorithms. The kubelet tlsMinVersion field and the --tls-min-version parameter on the kube-apiserver enforce a minimum TLS protocol version floor for inbound connections. The Antrea networking component and vSphere Cloud Provider Interface on VKS clusters also support configurable TLS cipher suites for component-to-component communication. Kubernetes hardening guidance identifies specific preferred cipher suites and calls out cipher suite configuration on the kube-scheduler as a required hardening step. VKS clusters support the Istio service mesh package, which provides mutual TLS between workloads within the mesh; the meshMTLS.minProtocolVersion setting controls the minimum protocol version for inter-service communication, defaulting to TLS 1.2 with support for configuring TLS 1.3.
-Data-in-transit protections using TLS have customizable PKI keypair and certificate options. These range from fully automated within VCF to semi-automated using certificates from enterprise PKI infrastructure or fully custom certificates installed manually. Automated certificate issuance is supported with Microsoft Active Directory Certificate Services. Trust establishment uses standard PKI management with multiple certificate options including Root CA certificates, CSR-based certificates, and direct certificate uploads. VCF Operations provides centralized certificate lifecycle management for all VCF components, enabling automated certificate renewal, monitoring, and replacement across the infrastructure. Organizations should be aware that if self-signed certificates and private keys are generated using OpenSSL, those certificates and private keys are not FIPS-compatible. Environments operating under FIPS requirements should use certificate authorities and key generation methods that produce FIPS-compliant artifacts. For FIPS environments, certificates should use key sizes of 2048 or 3072 bits; key sizes greater than 3072 bits have not been tested with FIPS. At the VKS layer, the cert-manager package manages the lifecycle of certificates issued to workloads and ingress endpoints. VKS clusters maintain TLS certificates for component-to-component communication across their control and data planes. The Contour ingress package supports minimum TLS version configuration through the tls.minimum-protocol-version parameter. Harbor, when deployed as a Supervisor Service, accepts custom TLS certificate configuration through the tlsCertificate.tls.crt and tlsCertificate.tls.key fields, allowing organizations to supply certificates from their enterprise certificate authority rather than relying on self-signed certificates. The Supervisor secret injection agent automatically configures mutual TLS for communication with the vault-agent-injector service using auto-generated certificates.
-Data-at-rest encryption uses vSAN cluster-based encryption or VM Encryption on non-vSAN storage. vSAN encryption uses AES-NI CPU offloading for efficient processing, and VMware ESX hosts encrypt vSAN disk data using the industry standard AES-256 XTS mode. Encryption keys are managed through KMIP 1.1-compatible external Key Management Servers (KMS) or vSphere Native Key Provider (NKP), which is included in all vSphere editions and does not require an external key server. VCF implements a three-element domain of trust comprising the key provider, VMware vCenter, and vSAN hosts. Key Encryption Keys (KEK) wrap Disk Encryption Keys (DEK) for secure key management; ESX hosts use the KEK to encrypt their internal keys and store only the encrypted internal keys on disk, not the KEK itself.
-VCF Standard Key Providers have key wrapping capabilities that let organizations store a single wrapping key in their KMS, protecting multiple Key Encryption Keys within the VCF environment. This creates a three-tier key hierarchy: the Data Encryption Key encrypts object data, the Key Encryption Key protects the DEK, and the wrapping key protects the KEK. This approach reduces the number of keys stored in external KMS systems while maintaining cryptographic separation. Key wrapping includes automatic key rotation with configurable intervals from 30 days to 10 years.
-With key persistence enabled, ESX hosts can persist encryption keys in the Trusted Platform Module (TPM) across reboots, allowing encryption operations to continue when the key server is unavailable. Each ESX host obtains the encryption keys initially and retains them in its key cache; if the ESX host has a TPM, the encryption keys are persisted in the TPM across reboots. Key persistence can be enabled using the esxcli system security keypersistence enable command.
-VCF supports guest-level security features including virtual Trusted Platform Module (vTPM) 2.0 for VMs. This enables in-guest encryption capabilities such as Windows BitLocker, Linux disk encryption, and other operating system-native security features. Secure Boot provides UEFI verification to help ensure only signed and trusted code runs during the VM boot process. These features work independently of or in combination with infrastructure-level encryption, allowing organizations to implement defense-in-depth strategies.
-vSAN offers Data-in-Transit (DIT) encryption as a cluster-wide setting that encrypts all data and metadata traffic as it transits across hosts. For vSAN Original Storage Architecture (OSA), data-at-rest encryption occurs at the Local Object Manager (LSOM) layer on the target host, making DIT encryption strongly recommended to restrict network-level interception. For vSAN Express Storage Architecture (ESA) in HCI mode, data is encrypted at the VM host before network transmission, making DIT encryption optional based on compliance requirements and risk tolerance. DIT encryption operates without requiring external key management servers and provides independent key rotation from data-at-rest encryption.
-Encrypted vSphere vMotion secures confidentiality, integrity, and authenticity of data transferred during VM migrations. For encrypted VMs, vMotion always uses encryption. For unencrypted VMs, encrypted vMotion can be set to Disabled, Opportunistic (default), or Required. Cross-vCenter vMotion is supported when using shared key providers or backup/import of Native Key Provider. VCF uses one-time keys (nonces) for each migration session so that captured traffic cannot be replayed or decrypted after migration completes.
-Memory Tiering encryption provides protection for tiered memory without requiring external key management. VCF generates random 256-bit AES-XTS keys at the kernel level during VM power-on, unique to each VM instance or per host depending on configuration.
-VM Encryption provides protection across all datastore types including vSAN, iSCSI, NFS, and Fibre Channel. Disk encryption uses XTS-AES-256 keys as the disk encryption key. This encryption occurs before data reaches the storage layer, providing both data-at-rest and data-in-transit protection.
-Kubernetes on VKS supports encryption at rest for data stored within the control plane. Operators configure the encryption provider and manage key access for control plane secrets; when relying on a managed key provider, administrators retain responsibility for access controls over the managed key material. The VCF Automation consumption layer includes VCF Encryption Management, which grants organization administrators the ability to use encryption keys from their own key providers for encryption of virtual machines and disks in their VCF environment, extending the platform's cryptographic key management to tenant-level operations.
-For storage protocols, VCF provides varying levels of native encryption support. iSCSI includes CHAP for session authentication. Fibre Channel Gen 7 supports end-to-end encryption with secure HBAs. For NFS datastores, version 4.1 supports Kerberos authentication with three security levels: krb5 (authentication only), krb5i (authentication plus integrity checking), and krb5p (authentication plus privacy with full encryption).
-ESX stores configuration data in encrypted form on boot devices. When the host has a TPM 2.0 enabled and configured, the configuration encryption key is stored in the TPM. The encryption mode can be configured using the esxcli system settings encryption set command with the --mode=TPM parameter.
-Cryptographic operations are controlled through fine-grained privileges in vCenter. Only users assigned the Cryptographic Operations privileges can perform cryptographic operations. A dedicated No Cryptography Administrator role enables standard VM and infrastructure management while restricting unauthorized encryption changes. This role can be cloned and customized to grant only specific Cryptographic Operations privileges, such as allowing encryption but not decryption, supporting the principle of least privilege for encryption tasks. The CryptoManager and CryptoManagerKmip managed objects provide programmatic interfaces for handling cryptographic keys and integrating with key management server infrastructure. vSAN encryption key management requires specific permissions including Cryptographer.ManageEncryptionPolicy, Cryptographer.ManageKeyServers, and Cryptographer.ManageKeys.
-vSAN includes secure disk wipe capabilities for proper media sanitization when decommissioning storage, supporting the Erase disks before use option during encryption configuration and disk management operations.
-Defining the organization's cryptographic policy (algorithm selection, key strength, rotation schedules, KMS architecture, FIPS-mode activation decisions) and the key lifecycle management standards that govern key creation, distribution, storage, archive, and destruction sit with the organization above the platform. VCF supplies the validated cryptographic modules and protocol enforcement; the organizational cryptographic governance program determines how those mechanisms apply across the environment. Security Technical Implementation Guides (STIGs) for Supervisor and VKS releases are available to guide cryptographic hardening of the consumption layer.
-VMware Private AI Services (PAIS) provides cryptographic controls across its AI infrastructure components, building on the cryptographic foundation of VCF.
-GPU-accelerated VMware Kubernetes Service (VKS) clusters deployed for PAIS workloads use a FIPS-enabled Kubernetes runtime. The VKS cluster topology version applied to both control plane and worker deployments uses a FIPS-enabled VKR build running on Ubuntu 24.04, so AI workloads on PAIS VKS clusters operate within a FIPS-compliant Kubernetes runtime.
-PAIS endpoints use TLS for service communication. The PAISConfiguration custom resource supports configurable CA bundle references through spec.clientTls.caBundleRefs for OIDC provider and Harbor registry authentication. The Supervisor endpoint communication for PAIS uses HTTPS on port 6443 with certificate-based authentication. The PAIS Prometheus metrics endpoint uses self-signed certificate authentication with TLS, where the CA certificate is retrieved from the pais-ingress-default Secret in the PAIS namespace and configured in base64-decoded form. Prometheus TLS client authentication and certificate validation are off by default; auditors should verify that client authentication is enabled in production deployments where mutual certificate validation is required.
-PAIS requires CA trust bundles to be configured for all external HTTPS connections, including OIDC providers, Harbor registries, content management systems used as data sources in the Data Indexing and Retrieval service (such as Confluence or SharePoint), MCP servers that provide tools to agents, and the pgvector database server used for vector storage. Trust bundle material is obtained from each external system's administrator either as a certificate file or as a ConfigMap stored in the namespace where PAIS is deployed, and PAIS recommends maintaining separate trust bundles per application with periodic updates before certificate expiration. Administrators add trusted certificates through the VCF Automation Provider Management UI under Certificate Management and Trusted Certificates. The issuer certificate of the Harbor registry must also be added to the certificate trust store on Deep Learning VMs that pull models from the registry. When connecting to an MCP server over HTTPS, the MCP server issuer certificate must be added as a CA trust bundle.
-The underlying cryptographic algorithms, cipher suites, and platform-level key management are provided by VCF and VKS. Organizations are responsible for selecting and enforcing approved cryptographic standards at the VCF and infrastructure level, while PAIS provides the certificate management and trust chain configuration mechanisms specific to AI service endpoints.</t>
+          <t>VCF provides cryptographic protection for data in transit across management, compute, storage, and inter-site networks. The architecture applies encryption at multiple layers using validated cryptographic modules and current TLS protocol versions.
+VCF management and monitoring communications use TLS as the transport protocol. VCF Operations for Networks supports modern TLS protocol versions, with the ability to restrict cryptographic module usage to FIPS-validated modules by enabling FIPS mode for external connections. Telegraf, the metrics collection agent, is configured to require a modern minimum TLS version for its communication channels. When using the databus for on-premises environments, HTTPS is the recommended transport to protect data during transmission and to verify subscriber authenticity. The TLS implementation includes customizable PKI options ranging from fully automated certificate management within VCF to integration with enterprise PKI infrastructure such as Microsoft Active Directory Certificate Services. VCF Operations provides centralized certificate lifecycle management across VCF components, supporting auto-renewal for VMCA, MSCA, and OpenSSL CA, handling automated renewal, monitoring, and replacement. Machine SSL certificates can be renewed through the API for a specified period up to 730 days. Starting in vSphere 9.0, all vSphere TLS profiles are FIPS compliant, and the COMPATIBLE profile supports modern TLS cipher suites and elliptic curves. The vCenter appliance uses VMware's Boring Crypto Module version 6.0, which provides FIPS-validated cryptographic operations including AES, ECDSA, HMAC, RSA, and SHA-2 variants.
+NSX, which provides networking services within VCF, uses FIPS 140-3 validated cryptographic modules by default. These modules are validated through the NIST Cryptographic Module Validation Program. NSX Manager uses FIPS 140 approved algorithms for authentication to its cryptographic module. For site-to-site connectivity, the NSX L2 VPN FIPS compliance suite uses FIPS-approved encryption with Perfect Forward Secrecy enabled and standardized Diffie-Hellman key exchange, providing transmission confidentiality for tunneled traffic. VCF Operations for Networks supports modern ECDSA and RSA signature algorithms for data source connections.
+VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module, which is compliant with FIPS 140-3 (Certificate #4743). VCF Operations for Networks uses the BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 with FIPS 140-2 Certificate #37009. These validated modules underpin the cryptographic operations used for securing communications across the automation and operations components.
+At the storage layer, vSAN provides data-in-transit (DIT) encryption that protects data as it moves between hosts within the cluster. DIT encryption is a cluster-wide setting that, when enabled, encrypts all data and metadata traffic across hosts. Forward secrecy is enforced for vSAN data-in-transit encryption, meaning that compromise of a long-term key does not expose previously encrypted traffic. DIT encryption operates independently of data-at-rest encryption and does not require external key management servers. The behavior differs by storage architecture: in vSAN Original Storage Architecture (OSA), data-at-rest encryption occurs at the target host's Local Object Manager layer, so data traverses the network before encryption, making DIT encryption strongly recommended. In vSAN Express Storage Architecture (ESA) in HCI mode, data is encrypted at the VM host before network transmission, making DIT encryption optional based on compliance requirements.
+VM Encryption provides confidentiality protection across all datastore types including vSAN, iSCSI, NFS, and Fibre Channel. VM encryption is implemented on the ESX host rather than on the storage array, so it protects data both at rest and in transit to the storage backend. Disk encryption uses AES-256 as the disk encryption key.
+Encrypted vSphere vMotion protects VM data during live migrations. For encrypted VMs, vMotion always uses encryption and cannot be disabled. For unencrypted VMs, encrypted vMotion offers three settings: Disabled, Opportunistic (default, uses encryption when supported), and Required. AES-NI significantly improves encryption performance for these operations. Cross-vCenter vMotion supports encryption when source and destination use shared key providers; vCenter Crypto Manager provides an importProvider method to import a vSphere Native Key Provider configuration between sites. vSphere Fault Tolerance log traffic, which synchronizes VM state between primary and secondary instances, can also be encrypted to protect this synchronization data in transit.
+Storage protocol support varies by type. vSAN File Service supports NFS4 Kerberos authentication with security options krb5, krb5i, and krb5p, where krb5p provides authentication plus encryption of data in transit. iSCSI uses CHAP for session authentication but does not encrypt data natively, so VM Encryption or in-guest encryption is needed for confidentiality on iSCSI networks. Fibre Channel Gen 7 supports end-to-end encryption with secure Host Bus Adapters.
+HCX Network Extension services support transport encryption for data between site pairs, and this encryption is enabled by default. VCF Operations HCX tunnel encryption similarly uses transport encryption by default to protect Network Extension data and migration traffic between sites. This default-on approach reduces the risk of data being transmitted in cleartext during workload migrations or network extensions.
+High-quality entropy generation on ESX hosts supports the proper functioning of security-related operations such as generating encryption keys for secure network communication. This foundational capability helps maintain the strength of cryptographic keys used across all transmission encryption functions in the platform.
+VMware Kubernetes Service (VKS), which runs on vSphere Supervisor, applies TLS encryption across all control-plane communication paths. The Kubernetes API server enforces encrypted transmission within the control plane and between the control plane and its clients by default, so all API server interactions travel over TLS. Cipher suites are configurable at each component layer: the kube-apiserver `--tls-cipher-suites` parameter accepts a comma-separated list of permitted cipher suites; the kube-scheduler exposes the same `tls-cipher-suites` parameter to keep its API endpoint aligned; and the kubelet exposes `tlsCipherSuites` and `tlsMinVersion` settings in `KubeletConfiguration` to scope the permitted cipher algorithms and minimum protocol version at the node level. Antrea, the CNI plugin included with Supervisor, supports configurable TLS cipher suites for its own secure communication channels through the `tlsCipherSuites` setting, and the vSphere Cloud Provider Interface (CPI) exposes the same capability through a configurable cipher suite list.
+For environments with strict cryptographic requirements, VKS supports FIPS mode through the ClusterClass variable `fips.enabled`, which controls which encryption algorithms are permitted at the node level. TanzuKubernetesRelease references carrying the `-fips.1` suffix indicate that FIPS cryptographic modules are active for that node pool. The Istio service mesh package, available as a standard package on VKS clusters, ships with FIPS compliance and supports mutual TLS (mTLS) between pods within the mesh; the `meshMTLS.minProtocolVersion` setting controls the minimum acceptable protocol version for all inter-service traffic. Ingress-layer encryption for workloads is handled by the Contour package, which exposes `tls.minimum-protocol-version` and `tls.maximum-protocol-version` settings so operators can define a bounded range of acceptable protocol versions for inbound HTTPS traffic. The Supervisor secret injection agent automatically configures mutual TLS for its communication with the vault agent injector service using auto-generated certificates. Harbor, available as a Supervisor Service, accepts custom TLS certificates through its `tlsCertificate.tls.crt` and `tlsCertificate.tls.key` configuration fields, supporting encrypted access to the container registry for image distribution.
+Defining the encryption policy for customer workload traffic, selecting cipher and FIPS configurations for environments with stricter requirements, and validating that data transmitted from customer applications and containerized workloads meets confidentiality standards are organizational data-policy decisions.
+VMware Private AI Services (PAIS) provisions VKS clusters using a FIPS-enabled Kubernetes build for cryptographic compliance across both control plane and worker node communications. The VKS cluster topology version is v1.33.1--vmware.1-fips-vkr.2 with FIPS compliance enabled, running on an Ubuntu 24.04 OS image, covering the cryptographic modules that protect data in transit within the cluster fabric.
+PAIS, activated through the PAISConfiguration custom resource on the Supervisor, requires HTTPS for all external integrations. The spec.clientTls.caBundleRefs section of the PAISConfiguration YAML references CA trust bundles supplied as ConfigMap resources. Operators must configure HTTPS trust bundles for the OIDC provider, the Harbor container registry, content management systems hosting Knowledge Base data sources, MCP servers providing tools to models, and the pgvector database. Separate trust bundles are recommended per application, with periodic updates required before certificate expiration.
+The PAIS Supervisor endpoint uses HTTPS on port 6443 with certificate-based authentication. The PAIS ingress endpoint is protected by a self-signed certificate stored in the pais-ingress-default Kubernetes Secret. Administrators retrieve the CA certificate using `kubectl get secrets/pais-ingress-default -o yaml` and distribute it to clients that connect to the service, including Grafana when configured to scrape the PAIS Prometheus endpoint. CA trust bundles for external entity connections are managed through ConfigMaps and updated as certificate content changes.
+VCF Automation Provider Management for PAIS uses a base64-encoded certificate (TM_CERT_BASE64) obtained by running openssl s_client against the VCF Automation FQDN on port 443, enabling authenticated HTTPS communication between AI catalog tooling and the PAIS environment. MCP server integrations require the MCP server's issuer certificate to be added as a CA trust bundle before connecting over HTTPS using either Streamable HTTP or Server-Sent Events transport.
+Telemetry sent from PAIS to the OpenTelemetry Collector is authenticated using a Kubernetes Secret containing Authorization Bearer tokens and custom authorization headers. LLM trace transport to the collector uses HTTP/protobuf or gRPC, both protecting trace traffic in transit.
+One configuration detail that auditors should verify: PAIS Prometheus TLS client authentication and certificate validation are turned off by default (the tls-client-authentication setting on the Prometheus endpoint). Organizations should review this setting and enable mutual TLS where their policy requires it. The underlying network transport encryption between VMs and workload domains is provided by VCF and is documented in VCF Coverage.</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -845,14 +855,10 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to the implementation of cryptographic protection controls by using known public standards and trusted cryptographic technologies across its component stack for securing inter-component communications and providing cryptographic inspection capabilities for network traffic.
-Security Services Platform (SSP), the control-plane component of vDefend, secures communications between vDefend product components using certificates and current TLS protocol versions with approved cipher suites. SSP and the SSP Installer deploy with the most current TLS version by default and also support the prior major TLS version. The TLS versions and cipher suites allowed on SSP Installer and SSP are fixed and cannot be modified, which enforces a consistent cryptographic baseline across deployments.
-SSP components, including the SSP Installer and the NDR Sensor for vDefend, implement FIPS 140-2 and FIPS 140-3 cryptographic module standards. SSP uses the VMware BouncyCastle Module (NIST CMVP Certificate #4943) and the VMware OpenSSL FIPS provider Object Module (NIST CMVP Certificate #4861) for its cryptographic operations. SSP actively enforces cryptographic hygiene by rejecting any certificate or TLS configuration that uses deprecated algorithms, short keys, or legacy protocol versions, returning a validation error rather than permitting degraded connections.
-Certificate management within SSP provides lifecycle controls including certificate export, certificate signing request (CSR) generation, and CA-signed certificate replacement. SSP monitors and manages several certificate types used to identify client and host machines, establish trust between components, secure communications, and control access levels. Administrators can retrieve and validate LDAP certificates using standard tools to establish secure LDAPS connections for platform authentication. These capabilities allow organizations to integrate vDefend into their broader PKI infrastructure and follow standard certificate lifecycle practices.
-vDefend provides TLS Inspection capabilities that allow the firewall to decrypt, inspect, and re-encrypt TLS-protected traffic. Without TLS Inspection, encrypted traffic cannot be examined or enforced against security policies even when other advanced security features are enabled. With TLS Inspection enabled, vDefend gains visibility into encrypted traffic flows, supporting more effective access control and threat detection. TLS Inspection also supports importing or generating trusted and untrusted proxy certificate authorities for external decryption profiles, giving administrators control over the CA chain used in inspection.
-TLS Inspection includes a Crypto Enforcement option within decryption action profiles that allows administrators to set minimum and maximum protocol version and cipher suite constraints for both client and server connections. Profiles can be configured in Transparent or Enforce modes; the Enforce mode requires compliance with the configured cryptographic constraints.
-vDefend IDS/IPS signature rules extend cryptographic visibility by supporting protocol version matching and certificate Subject field matching, enabling enforcement decisions based on certificate metadata in encrypted traffic. IDS/IPS rules also support storing TLS/SSL certificates to disk for forensic analysis and threat investigation. SSP guidance recommends that organizations restrict or block protocols that carry data in cleartext and enforce minimum secure protocol versions as part of their network security practices.
-vDefend does not itself provide the underlying key management infrastructure (KMS), platform-wide PKI lifecycle management, or the broader VCF platform's cryptographic controls; those responsibilities belong to VCF. However, vDefend's consistent use of approved cryptographic standards for its own operations and its ability to perform cryptographic inspection of network traffic contribute to an organization's overall implementation of cryptographic protection controls.</t>
+          <t>VMware vDefend contributes to transmission confidentiality through inspection, visibility, and enforcement mechanisms at the network layer, while the underlying cryptographic protection of data in transit is the responsibility of endpoint applications and infrastructure components.
+TLS Inspection uses a transparent TLS proxy to intercept and analyze encrypted traffic flows traversing the environment. This allows security policy to be applied to traffic that would otherwise be opaque and supports detection of threats embedded within encrypted sessions. TLS Inspection can be deployed to provide visibility into encrypted connections while preserving end-to-end encryption for flows not subject to a decryption policy, and supports both inbound and outbound inspection profiles.
+Security Intelligence, integrated within the Security Services Platform (SSP), surfaces workloads communicating over application protocols that transport data without encryption. The Security Segmentation Report identifies communication chains containing at-risk unprotected members and quantifies the number of unprotected data flows hitting default-allow rules across observed traffic. Administrators can use this reporting to identify and prioritize remediation of encryption coverage gaps, including restricting or blocking cleartext protocols.
+The Security Services Platform and its component services use FIPS 140-2 and FIPS 140-3 validated cryptographic modules for their own communications. Network Detection and Response (NDR) Sensors connect to the SSP using mutual TLS authentication (mTLS), with a dedicated certificate for each sensor signed by an intermediate certificate authority on the SSP. The SSP can be configured to forward log messages to a syslog server over TLS, and Malware Prevention Service remote logging likewise uses TLS to transmit log data to a remote log server. NDR also supports SSL verification for event logs sent over HTTPS. When NDR shares data to the cloud, it anonymizes sensitive customer information before transmission.</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -862,11 +868,9 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) implements cryptographic protections for disaster recovery workflows using known public standards and trusted cryptographic technologies.
-PNR uses modern TLS by default for all connections to the PNR server. The minimum TLS protocol version is configurable through the envoy-proxy-config.json file by editing the tls_minimum_protocol_version parameter. When the minimum protocol version is modified, PNR requires that the change be applied consistently across all relevant configuration occurrences in the system. Administrators can verify the TLS version in use on the Site Recovery Manager component using standard OpenSSL tooling.
-The PNR Appliance requires an SSL/TLS certificate as the endpoint certificate for all TLS connections to the PNR server. PNR supports custom certificates signed by a certificate authority as an alternative to self-signed certificates. Custom SSL/TLS server endpoint certificates must meet specific requirements, including x509v3 Extended Key Usage indicating TLS Web Server Authentication. The Appliance Management Interface allows administrators to import CA-signed server certificates and custom root CA certificates, and to replace the appliance certificate. PNR uses TLS certificates and private keys to protect network communication and establish authentication with other servers. Certificate verification error messages are logged in security-related log files, and operational log files do not contain sensitive information such as private keys or passwords.
-For encrypted virtual machine replication, PNR requires that the recovery and protected sites use a common Key Management Server (KMS) or that the KMS clusters at both sites share common encryption keys. Replication of encrypted virtual machines also requires Secure LWD support to be available on the virtual machine. This supports data-at-rest encryption continuity for virtual machines through the recovery lifecycle.
-Defining the organization's cryptographic policy, including KMS architecture decisions, minimum TLS version selection, certificate management standards, and key lifecycle practices, sits with the organization above the DR layer. PNR supplies the cryptographic mechanisms needed for DR-specific traffic and operations; the organizational cryptographic governance program determines how those mechanisms apply across the environment.</t>
+          <t>VCF Protection and Recovery (PNR) applies cryptographic protection to the channels through which it manages paired sites and moves data between them. PNR uses TLS certificates and private keys to protect network communication and to authenticate with peer servers. The Protection and Recovery Appliance terminates TLS through an envoy proxy, and the minimum TLS protocol version is configurable by editing the tls_minimum_protocol_version parameter in the envoy-proxy-config.json file. Replication of virtual machine data between sites supports optional network-level encryption, and PNR can protect and recover virtual machines that are themselves encrypted, applying that protection through both array-based protection groups and vSphere Replication protection groups.
+Authentication to vCenter and to remote PNR sites is brokered through VCF SSO. PNR acquires a holder-of-key SAML token from VCF SSO and presents it in cryptographically signed requests to remote services. The Configure Remote Site workflow imports certificates of the remote vCenter to establish trust for the cross-site connection, and the appliance prompts for VCF SSO credentials when an operator initiates operations that affect both sites.
+PNR does not provide the network-layer VPN that connects paired sites. The product documentation requires that the connection between the local and remote sites of a Protection and Recovery pair be private, such as a VPN provisioned outside PNR. For isolated recovery environments used during cyber recovery operations, VMware recommends that workload user access be performed through VPN or a Remote Desktop Client rather than direct public internet exposure of recovered services.</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -876,12 +880,10 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) implements cryptographic protections across multiple layers of its architecture, applying standard cryptographic technologies for data in transit, certificate trust management, and credential storage.
-Starting with DSM, the platform enforces FIPS 140-3 compliant cryptographic standards and validates certificates during upload, rejecting unsupported algorithms or parameters. Only RSA and ECDSA public key algorithms are accepted for certificates. The Ed25519 elliptic curve signature algorithm is rejected because it does not comply with FIPS 140-3. Custom trusted certificates should use ECDSA P-256 or P-384 algorithms; RSA certificates must meet a minimum key size of 2048 bits per FIPS requirements. DSM's latest certificate validation mode enforces strict cryptographic and KeyUsage validations across all DSM endpoints, including the Provider VM and data service clusters.
-For connections to database clusters, DSM requires TLS for all client traffic. PostgreSQL database instances enforce a minimum TLS protocol version through the ssl_min_protocol_version setting. MySQL enforces minimum TLS versions on both the main connection interface and the administrative interface; these settings are fixed and cannot be modified by users, which helps maintain a consistent cryptographic baseline across deployments. MySQL also exposes the group_replication_recovery_tls_version setting to specify the TLS protocol used during distributed recovery connections. DSM supports SQL Server clusters, which use TLS to encrypt communication between clients and the cluster; the network.tlsProtocols custom engine setting defines the allowed TLS versions for client connections, and a minimum TLS version must be included for the DSM operator to manage the cluster. DSM supports TLS verification during PostgreSQL database migration, covering replication traffic between source and target clusters.
-DSM's certificate management capabilities support standard PKI practices. Administrators configure custom TLS certificates for database clusters through the DSM UI or API, providing certificates in PEM format with associated private keys and CA certificates. Supported private key algorithms are RSA and ECDSA with key sizes of 256 and 384 bits. When present, the X509v3 KeyUsage extension on a custom certificate must include the DigitalSignature capability; DSM also accepts certificates that omit the KeyUsage extension entirely, treating absent KeyUsage as permitting all usages in accordance with RFC 5280. To establish secure connections to database clusters and to the DSM Provider VM, clients add the CA to the operating system trust store or the trusted CA list. DSM's API provides a mechanism to retrieve the CA certificate from a custom certificate secret. The Consumption Operator, which enables self-service database provisioning, requires a TLS certificate for its communication with the DSM provider. Certificate management can also be handled through Kubernetes cert-manager, which manages various issuer types and outputs Kubernetes TLS Secrets in the format DSM requires.
-DSM supports TLS for connections to external systems. When configuring log forwarding to an SMTP server, DSM supports Auto TLS to establish a secure connection. For private container registries, DSM supports CA certificate validation for untrusted registries.
-For local user credential storage, DSM encrypts passwords using PGP symmetric encryption through the PGCrypto library, with dedicated encryption keys stored using the PGCRYPTO_PASSWORD and PGCRYPTO_ALGORITHM keys. MySQL has FIPS mode available on the client side through the ssl_fips_mode setting. PostgreSQL databases include the pgcrypto extension, which provides cryptographic functions that applications can use directly within the database. The DSM Provider Appliance includes virtual machine encryption, which activates when a Key Management Server is configured in the environment.</t>
+          <t>VMware Data Services Manager (DSM) applies TLS-based encryption across multiple communication paths, covering database client connections, management interfaces, service-to-service communication, and data migration traffic. Starting with DSM, the platform enforces FIPS 140-3 compliant cryptographic standards and validates certificates during upload, rejecting unsupported algorithms such as Ed25519.
+For database client connections, DSM enforces a minimum TLS protocol version across all supported database engines. PostgreSQL instances enforce a configurable minimum TLS protocol version via the `ssl_min_protocol_version` setting and support certificate-based authentication with CA verification. PostgreSQL replication connections support SSL/TLS encryption with a configurable `sslmode` parameter to secure data in transit between source and target databases, and DSM validates SSL trust before establishing replication. MySQL locks TLS protocol enforcement at the platform level so users cannot weaken it. MySQL has `require_secure_transport` set to ON by default, which requires all client connections to use encrypted transport. MySQL supports FIPS mode via the `ssl_fips_mode` setting. DSM adds SQL Server as a supported database engine; SQL Server clusters use TLS to encrypt client connections, require a minimum TLS version for DSM operator management, and expose the `network.tlsProtocols` engine setting to configure the set of allowed TLS versions.
+For management and service-to-service communication, the DSM Provider exposes an HTTPS endpoint. The Consumption Operator requires a TLS certificate for secure communication with the DSM provider. In network-isolated deployments, Consumption Operator image transfers to a private registry support optional TLS certificate authentication. Metrics forwarding from DSM to VCF Operations supports mutual TLS (mTLS) authentication, requiring a client certificate and private key. DSM SMTP settings include an Auto TLS option that establishes a secure connection to the SMTP server.
+DSM provides certificate management capabilities to support the TLS infrastructure. Custom certificates are validated for FIPS 140-3 compliance at upload time; accepted key types are ECDSA P-256, ECDSA P-384, and RSA with a minimum key size of 2048 bits, and Ed25519 keys are rejected as non-compliant. Trusted root certificates added through the DSM UI must comply with FIPS requirements.</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
@@ -891,12 +893,12 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides configurable SSL/TLS profiles that control which cipher suites, protocol versions, and key exchange algorithms are permitted for application traffic termination. The SSL/TLS Profile, configured under Templates &gt; Security &gt; SSL/TLS Profile, contains the accepted protocol version list and a prioritized cipher suite list applied to virtual services. Administrators can create custom profiles or select from built-in templates; the documentation notes that the choice of accepted ciphers and protocol versions involves trade-offs between security, client compatibility, and computational expense. SSL profiles in 9.1 include a Post Quantum Cryptography section with support for modern cipher suites. Controller SSL/TLS certificates support elliptic curve (EC) or RSA algorithms, with EC recommended for new deployments.
-For environments subject to cryptographic module validation requirements, Avi supports a FIPS mode backed by the OpenSSL FIPS Provider, which has been validated at FIPS 140-3 Security Level 1 and awarded Certificate #4985 by the Cryptographic Module Validation Program (CMVP). When FIPS mode is activated on the Controller cluster, Avi restricts cryptographic operations to FIPS-compliant algorithms only. FIPS 140-3 also requires stricter handling of sensitive security parameters including keys, authentication data, and random number generation. FIPS mode is enabled at the Controller cluster level through the Controller settings. Note that FIPS mode does not support SSL Client Hello events in Avi DataScript, which may affect certain scripted traffic inspection use cases.
-Avi Controller allows administrators to restrict specific key exchange algorithms and ciphers for management session access. The Allowed Ciphers field restricts management session ciphers to a specified subset, and the kex_algorithm_exclude field under Controller Settings excludes specific key exchange methods for SSH-based administrative access. Internal communications between the Avi Controller and Service Engines also use SSL/TLS, and custom certificates can be selected for this Secure Channel connection via the Access tab certificate field.
-For certificate management, Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. The Controller is set up as an HSM client and can create keys and certificates directly on the HSM through client libraries, supporting high-availability HSM configurations. Automated certificate lifecycle management is available through Let's Encrypt integration using the ACME protocol. Avi's App Transport Security feature supports integration with the Venafi Trust Protection Platform for certificate administration across tenants, with the Trust Protection Platform pushing signed certificates and required chain certificates to Avi Load Balancer.
-For Kubernetes deployments, the Avi Kubernetes Operator (AKO) supports PKIProfile-based certificate validation and trust management for backend services. The PKIProfile, configured through custom resources, enables secure communication with backend services through certificate-based authentication and encryption. In VCF environments, the Avi PKI Profile defines the list of trusted certificate authorities permitted to sign client certificates and can be used to implement Zero Trust security between servers and clients.
-Data-at-rest encryption for Avi Controller and Service Engine VMs is provided by VCF at the platform layer, not by Avi itself. Organizations must configure Avi SSL/TLS profiles, select appropriate cipher suites, and enable FIPS mode where cryptographic module validation requirements apply to activate these controls.</t>
+          <t>VMware Avi Load Balancer provides application-layer network security policy mechanisms that help organizations implement network access controls at the application delivery boundary. These Avi-native capabilities operate at the Virtual Service level and give administrators structured objects for defining, governing, and updating access rules as requirements change.
+Avi's Network Security Policy evaluates incoming client traffic based on network-level parameters and determines whether a connection should be accepted, discarded, or rate-limited. IP Group-based access control lists applied per Virtual Service are the most scalable method for implementing network-layer ACLs, allowing administrators to specify which source addresses may reach individual application services. Policies can be created and modified through the Avi Controller CLI using the configure networksecuritypolicy command, and updated programmatically through the REST API using the Modify Network Security ACL endpoint and IP Group UUID references.
+Starting with Avi Load Balancer version 32.1, NSX security groups can be used directly in both HTTP Policies and Network policies. Security groups defined once in NSX are reused across Avi Virtual Service security policies, removing the need to manually maintain IP address lists in Avi. When an IP address changes in NSX, the update propagates automatically to Avi Load Balancer, keeping Virtual Service security policies current without manual intervention. This integration provides a unified governance model where network security group membership is managed centrally in NSX and reflected automatically in Avi policy enforcement.
+Avi's DDoS Policy detects and mitigates Layer 4 through Layer 7 network attacks through the Network Security policy framework, providing additional network security control at the application delivery layer.
+Within the broader VCF platform, NSX provides underlay routing and network infrastructure for Avi Service Engines. East-west firewall enforcement between application tiers is provided by VMware vDefend, a separate product that extends the platform's network security posture beyond what Avi provides at the application proxy boundary.
+Satisfying this control fully requires the organization to document procedures for governing and updating network security controls across the Avi tier and the broader platform, assign ownership of Avi policy objects, and establish change management processes covering both Avi Network Security Policies and VCF-layer controls.</t>
         </is>
       </c>
     </row>
@@ -928,23 +930,23 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several technical mechanisms that help organizations restrict access to sensitive and regulated data based on job function, though the determination of which data qualifies as sensitive and which individuals require access remains an organizational responsibility.
-VCF's role-based access control (RBAC) model is the primary mechanism for limiting data access. Within VMware vCenter, administrators can define roles with granular privileges and assign them to individual users or groups on specific inventory objects. The platform follows the principle of least privilege: user accounts should be given the minimal number of privileges on the system that they require to do their jobs. If a predefined role does not meet an organization's needs, administrators can define a new role containing only the minimum set of required privileges. This allows organizations to tailor access so that personnel interact only with the data and resources their role demands.
-VCF Operations enforces privilege-based access controls over collected monitoring data. Users without appropriate privileges cannot view collected data for specific objects, and the platform cannot retrieve data that a user does not have permission to access. Role-based access also governs data management functions, where Admin and Member roles have different permissions for viewing and editing data retention settings and data source certificate validation. VCF Operations restricts viewing and using unassigned credentials to users with the required permissions.
-VCF Automation extends the RBAC model with organization-level access controls. Entity type access can be granted only to specific users and organizations, and organization-specific roles can be assigned only to users belonging to that organization. These roles contain a subset of the organization's rights, and organization users can exercise only those rights from their roles that have been published to their organizations. This layered restriction helps confine data access within organizational boundaries and functional scopes. Administrators can also add user criteria in the "Not Available For" field to restrict specific users from accessing particular projects or catalog items, and catalog item visibility depends on project membership.
-The Consumption layer of VCF, encompassing VMware Kubernetes Service (VKS) and the vSphere Supervisor, extends the RBAC model to containerized workloads and Kubernetes namespaces. Kubernetes RBAC allows administrators to define Roles that specify which operations (such as get, list, watch, create, update, or delete) may be performed on specific resource types within a namespace, then bind those Roles to users or service accounts via RoleBindings. ClusterRoles and ClusterRoleBindings extend this pattern to cluster-scoped resources. Supervisor enforces vSphere Namespace RBAC to restrict which users can connect to Supervisor and VKS clusters based on their assigned permissions; the guidance directs administrators to create least-privileged access even for cluster administrators, reserving elevated bindings for break-glass access. Access to node sub-resources through the kubelet API should be controlled using RBAC mechanisms and granted only when required, such as by monitoring services.
-Each vSphere Supervisor namespace serves as an access control boundary for multi-tenant workloads. Users and service accounts are bound to roles within specific namespaces, restricting them to resources only in their authorized namespaces. This supports separating workloads that handle regulated data from those that do not and limits lateral access across teams and applications. For external identity management, VKS clusters support integration with organizational identity providers such as Okta; the Okta integration exposes an Assignments &gt; Controlled Access configuration that restricts which organizational users can access specific VKS clusters, allowing job-function-based access restrictions to flow from the identity provider into Kubernetes RBAC. Harbor Registry, available as a Supervisor Service, secures container artifacts with policies and role-based access controls, restricting which users and service accounts can push or pull images that may contain sensitive configurations.
-Sensitive data protection is built into the platform at multiple levels. Sensitive information within HTTP-REST plug-in objects is considered internal to those objects and is not accessible through scripting properties and methods; administrators can store sensitive information in VCF Operations orchestrator configuration elements or in external password vaults, keeping such data out of general-purpose storage where broader access might exist. The platform guidance directs administrators not to store sensitive data such as passwords or private keys in plain text in data sets. The Supervisor encrypts all secrets stored in its etcd database, with the encryption key provided at boot by vCenter and stored in memory on Supervisor nodes and in encrypted form within the vCenter database.
-Within VKS clusters, Kubernetes Secrets provide a dedicated resource type for storing sensitive data, including credentials, API keys, certificates, and passwords, as Opaque-type objects. Secrets can be injected into pods as environment variables or volume mounts, and RBAC rules apply specifically to Secret resources to restrict read access to only the service accounts and users that require it. Developers can further restrict Secret access to specific containers within a pod. Using short-lived Secrets helps limit the window of exposure when secret data is disclosed inadvertently or otherwise, since expiration reduces the duration during which a compromised credential remains valid. Applications are expected to protect secret values after reading them from environment variables or volume mounts, including avoiding logging sensitive data in the clear or transmitting it to untrusted parties. Kubernetes and applications running within the cluster can take additional precautions such as avoiding writing sensitive data to nonvolatile storage. Confidential data should be stored in Secret resources rather than ConfigMaps, which do not carry the same independently configurable access restrictions. The Secret Store Supervisor Service adds a dedicated RBAC layer for sensitive data distribution, enforcing role-based access controls for administrators, DevOps engineers, and application tenants who manage and distribute secrets; this service stores sensitive data such as credentials, tokens, or access keys as encrypted values. For organizations that prefer to keep sensitive data outside the cluster, the Kubernetes Secrets Store CSI Driver enables pods to access confidential data from third-party secrets store providers. The Harness CI/CD integration supports HashiCorp Vault for this pattern, with secrets retrieved at deployment time rather than hardcoded in manifests or images. ValidatingAdmissionPolicies can further restrict permitted write actions on resources within sensitive workload namespaces, applying access constraints at the admission layer before objects are persisted to etcd. The etcd datastore itself should have controls to limit direct access and should not be publicly exposed.
-For particularly sensitive operations such as virtual machine encryption and decryption, vCenter provides fine-grained privilege separation through cryptographic operations privileges. Only users assigned these privileges can perform cryptographic operations. The No Cryptography Administrator role provides standard administrative privileges while withholding access to encryption, key management, and rekey operations. Administrators can clone this role and create custom roles that permit encryption but restrict decryption, or vice versa. This separation of duties approach limits who can access encrypted data and who can manage the encryption lifecycle. Administrators can also configure separate key providers for different departments or organizational units, enabling granular access control to encryption keys at a departmental boundary level.
-Data storage mechanisms within the platform also incorporate access controls. The vSphere Automation REST API organizes data into data sets with attributes that define access control and interoperability configuration, restricting which users and services can read or modify stored values. For vSAN file shares, the file service Customize net access option allows administrators to specify whether a particular IP address can access, make changes, or only read the file share, governing retrieval to authorized devices and users. The Datastore &gt; Browse datastore privilege governs which users or groups can view, upload, or download files stored on datastores, allowing administrators to restrict access to datastore file content to only those with a documented need.
-While VCF provides these technical enforcement mechanisms, the organizational processes that define data sensitivity classifications, determine which roles require access to which categories of data, and maintain ongoing access reviews must be established and managed outside the platform.
-VMware Private AI Services (PAIS) provides mechanisms that help restrict access to sensitive data used in AI workloads to authorized users.
-PAIS access is gated through OIDC group-based authorization. The PAISConfiguration custom resource accepts an authorizedGroups setting that names the identity groups permitted to use the service; user accounts that are not members of those groups are denied. The same gate applies whether activation is performed through the VCF Automation UI or through kubectl in the organization namespace, and it covers PAIS endpoints including Data Indexing and Retrieval.
-The Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. Project membership governs who can pull or push model artifacts, scoping who can retrieve fine-tuned models that may carry regulated content.
-For Knowledge Bases used by Data Indexing and Retrieval, each data source stores its own credentials and inherits the access boundary defined in the upstream system. Amazon S3 compatible store access keys configured as data sources must have permissions limited to listing and reading objects from the specified bucket. Confluence data sources authenticate using a user name and password or a personal access token configured under the Confluence administrator's settings. Microsoft SharePoint On-Premises data sources require user name and password authentication. Personal access tokens used for programmatic access to Knowledge Bases and their data sources are generated from individual user account settings, scoping API access to the issuing user.
-PAIS uses a configured CA trust bundle for secure communication with external services and databases, supporting authenticated connections to the systems that hold sensitive content.
-At the VCF Automation tenancy layer, region quotas assigned from selected supervisors and the assignment of non-reserved VM classes and storage classes for the PAIS organization control which resources are available to AI consumers, restricting which tenants can provision the Deep Learning VMs and VKS clusters that may process sensitive data.</t>
+          <t>VCF enforces role-based access control across all major platform components, restricting access to technology assets, applications, services, and data based on assigned roles with defined permissions. RBAC is applied consistently throughout the stack, covering compute management, networking, storage, operations management, automation services, and Kubernetes workloads.
+VMware vCenter provides fine-grained authorization through a permissions model that associates roles with users or groups on objects in the vCenter inventory hierarchy. Roles are sets of privileges, and vCenter defines three authorization levels: operator (read-only access to configuration, the most restricted level), administrator (read and write access to configuration but cannot manage user accounts, intended for users who alter vCenter configuration or exercise control functions), and super administrator (full control). When a predefined role is modified, the updated privilege set applies immediately to all users assigned that role. New roles are created with three default system-defined privileges (System.Anonymous, System.Read, System.View), and administrators add specific privileges to match the intended access level. vCenter also supports creation of custom roles with granular privilege assignment and permission propagation to vSphere objects in the inventory hierarchy.
+NSX implements RBAC by assigning users predefined roles with specific permissions. The platform includes 15 built-in roles: Enterprise Admin, Admin, Network Admin, Network Operator, Security Admin, Security Operator, Cloud Admin, Cloud Operator, Cloud Project Admin, Load Balancer Admin, Load Balancer Operator, VPN Admin, GI Platform Admin, NSX Platform Admin, and Support Bundle Collector. These roles follow the principle of least privilege, with each role carrying only the permissions needed for its functional area. NSX RBAC applies across multiple operational domains including inventory, plan and troubleshoot, and system management functions. NSX also supports project-scoped RBAC, where Network Admin, Network Operator, Security Admin, and Security Operator roles assigned within a project have permissions limited to that project's scope rather than the entire NSX system. This project-scoped model extends to VPCs and subnets within the NSX networking hierarchy. For organizations that need role definitions beyond the built-in set, NSX allows creation of custom roles tailored to specific operational requirements. Only an Enterprise Administrator can assign the role management permission to a custom role. NSX Federation extends RBAC to multi-site deployments, applying the same access control model across federated NSX instances. Principal identities, which are used for service-to-service authentication local to NSX, also support RBAC role assignment, so automated integrations operate under the same access control model as human users.
+VCF Operations enforces RBAC through the assignment of service roles to users and groups. Administrators configure role-based permissions through the Roles tab under Infrastructure Operations, where individual permissions can be selected or deselected to define what each role is authorized to do. The System Administrator role includes rights covering approvals, audits, certificates, datastores, edge clusters, integrations, LDAP settings, namespaces, proxy rules, system settings, tokens, and truststore operations. Administrative operations such as password management require authentication with a user assigned the ADMIN role. VCF Operations also defines its own roles within vCenter, with privileges named using a convention that appends the role to the product name (such as VCF Operations ContentAdmin Role and VCF Operations PowerUser Role). The PowerUser role has privileges to perform the actions of the Administrator role except for user management and cluster management. A further restricted PowerUserMinusRemediation role excludes remediation actions in addition to those limitations. A vCenter administrator assigns these roles to users, and VCF Operations maps vCenter users to the appropriate role.
+vSAN supports RBAC and permissions management for authentication and authorization of storage operations. The vSAN Security Configuration Guide provides guidance on configuring these role-based controls for storage infrastructure.
+VCF Automation governs access through multiple RBAC mechanisms at different scopes. At the organization level, rights bundles assign specific API permissions to roles including Organization Administrator, Organization Auditor, and Organization User. Group membership and role assignment are managed through the Access Control interface, and organization administrators can edit role assignments for groups at any time. At the project level, VCF Automation defines three distinct roles: administrators, members, and viewers, providing tiered access to project resources and operations. VCF Automation also governs blueprints, catalogs, content libraries, and custom entities through its role model. The Assembler Administrator role has read and write access to the entire user interface and API resources, while other roles have progressively narrower permissions.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS), VCF enforces RBAC through two complementary control layers. At the vSphere layer, vSphere Namespaces assign three permission roles: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). At the Kubernetes layer, the Kubernetes RBAC authorization framework governs access to all API server requests through four core objects: Roles define permissions scoped to a single namespace, ClusterRoles define permissions applying cluster-wide, and RoleBindings and ClusterRoleBindings associate those roles with authenticated subjects such as users, groups, or ServiceAccounts. Permissions are purely additive with no deny rules, and administrators can restrict access to individual resource instances by name using the resourceNames list in role rules.
+VKS clusters integrate with VCF SSO so that Kubernetes RoleBinding objects grant RBAC permissions directly to VCF SSO users and groups. This means the same identity provider that governs VMware vCenter access also governs Kubernetes cluster access, providing a consistent identity model across both the platform and workload layers. Cluster operators use kubectl or the Kubernetes API to assign role permissions to developers and other personas with defined responsibilities.
+Kubernetes RBAC also governs ServiceAccounts, which provide discrete identities for pods and automation processes. This separation allows human access and workload access to be governed independently, with each scoped to the minimum permissions required for its function. ServiceAccounts follow the principle of least privilege by receiving only the minimum set of permissions required to function correctly, and RBAC should be applied to Secret objects to enforce least-privilege access to sensitive data stored within namespaces.
+The Kubernetes RBAC API includes built-in controls against privilege escalation: the API prevents users from editing roles or role bindings to gain permissions beyond those they already hold, and this enforcement applies at the API level regardless of the authorization mode in use. Role-binding authority can be explicitly delegated by granting a user permission to perform the bind verb on a specific Role or ClusterRole, limiting the roles that identity can delegate to others.
+In multi-tenant VKS deployments, RBAC is the primary mechanism for isolating tenants within a shared cluster. Administrators use Role and RoleBinding objects at the namespace level to restrict each tenant's access to its assigned namespaces, and ClusterRole and ClusterRoleBinding objects to control access to cluster-level resources, blocking unprivileged users from crossing tenant boundaries.
+Supervisor services deployed on VKS clusters extend RBAC to their own access models. The Secret Store Supervisor Service enforces role-based access control across administrator, DevOps engineer, and application tenant roles, controlling who can manage and retrieve sensitive data. The Argo CD Supervisor Service implements RBAC through a configurable policy field using Casbin syntax, with the spec.rbac.policy setting defining role assignments and permission rules; policy rules (p rules) control account permissions including the ability to grant admin roles to specific local accounts, and group mappings (g rules) assign accounts to role groups.
+VMware Private AI Services (PAIS) provides role-based access control scoped to its AI services and AI workload delivery components. The central mechanism is OIDC group-based authorization for PAIS. When activating PAIS in an organization namespace, administrators populate the authorizedGroups setting with one or more OIDC group identifiers so that only users who belong to those groups can access the service. The OIDC configuration supports a configurable groups claim name through the oidc-groups-claim setting, with the groups claim carried in the Access Token and evaluated at access time. PAIS requires an OIDC provider configured as a public client application with Authorization Code and Refresh Token grant types, and it can be configured with one OIDC provider. Additional OAuth 2.0 client identifiers can be accepted by configuring Extra Audiences through the oidc-extra-audiences setting when the OIDC provider issues tokens for multiple audiences.
+PAIS extends the same identity model to the Grafana observability platform used for PAIS metrics. Grafana role assignment is configured through the grafana-oidc-role-mapping property using an expression such as contains(groups[*], 'pais-access-group') &amp;&amp; 'Admin' || 'Viewer', so OIDC group membership maps automatically to Grafana Admin or Viewer roles. PAIS uses the same OIDC provider for Grafana authentication that it uses for service access.
+For machine learning model storage, the Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as the model storage backend and requires authentication and certificate-based trust for model retrieval. PAIS is compatible with OCI-compliant registries from other vendors when deployed in a disconnected or air-gapped environment, and the project-scoped access controls apply to the chosen registry.
+Access to PAIS catalog items for GPU-accelerated VKS clusters and other AI workloads is governed through project-based permissions in VCF Automation. PAIS custom forms in blueprints can be modified to control user inputs at request time, scoping which configuration choices a requester can make when provisioning AI workloads. Knowledge Base data sources used by PAIS retrieval augmented generation require authenticated access to external repositories, including user name and password authentication for SharePoint On-Premises data sources and access keys with list and read permissions on the target bucket for Amazon S3 compatible stores. PAIS uses a CA trust bundle for secure communication with external services and databases.
+These PAIS-specific controls operate at the AI services and workload layer. Access to the underlying compute, storage, and networking infrastructure is governed by platform-level RBAC in VCF, including VCF SSO and VMware vCenter role assignments, and database-level access for vector and operational data is governed by Data Services Manager. PAIS adds service-level and workload-level RBAC for AI-specific assets on top of the VCF platform foundation rather than replacing those platform controls.</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -954,11 +956,12 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides network-layer mechanisms that contribute to protecting sensitive and regulated data transmitted to or from external Technology Assets, Applications and/or Services.
-The Distributed Firewall (DFW) and Gateway Firewall (GFW) enforce stateful east-west and north-south policies that restrict which workloads and data flows can reach external services. In VCF multi-tenant environments, Enterprise Administrators can configure Gateway Firewall isolation rules to deny all inter-project communication except designated infrastructure protocols, establishing strict network boundaries for applications that process regulated data.
-TLS Inspection extends this enforcement to encrypted external connections. vDefend External Decryption Action Profiles apply to encrypted traffic destined for external services not owned by the enterprise. Administrators can import or generate trusted and untrusted proxy Certificate Authorities for these profiles. The Crypto Enforcement option controls the permitted protocol versions and cipher suites for client and server connections, allowing administrators to block connections that do not meet minimum acceptable cryptographic standards for data in transit.
-Security Services Platform supports monitoring of application communication paths and segmentation posture. Security Intelligence administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment traffic flows, including flows toward external services. Security Services Platform Application Protection policies can be scoped to cover all application workloads, including critical applications handling regulated data. Security Services Platform guidance recommends restricting or blocking application protocols that transport data in clear text and enforcing minimum secure protocol versions, helping administrators identify and remediate data paths that lack adequate protection before data reaches external services.
-vDefend enforces the network-layer controls through which data protection requirements are implemented but does not govern contractual obligations with third parties, define data classification schemes, or establish the policies specifying which data requires protection.</t>
+          <t>VMware vDefend contributes to AAA governance through built-in controls in Security Services Platform (SSP) and through network-layer enforcement capabilities in the Distributed Firewall.
+SSP implements authentication using local accounts or directory-managed accounts. The platform uses Authelia, an open-source authentication and authorization server that provides two-factor authentication (2FA) and single sign-on (SSO) capabilities, alongside an Authserver that handles authentication requests and manages credentials. For directory integration, SSP supports Active Directory over LDAP or OpenLDAP, with only one identity source configured at a time. These capabilities apply across both the SSP platform itself and its License Hub component.
+For authorization, SSP ships with two predefined local user accounts that enforce separation of duties: an admin user with the Enterprise Admin role for full management access, and an audit user with the Auditor role for read-only access to APIs and services for system auditing. These accounts are present in the SSP platform, the SSP Installer, and License Hub. The audit user's password must meet required criteria and can be reset by the admin user through the User Management interface.
+For auditing, SSP provides a purpose-built audit user account scoped to compliance review and system inspection. All access events to License Hub are logged in audit logs that are enabled by default and cannot be disabled, providing a persistent access record for that management component.
+At the network enforcement layer, vDefend microsegmentation policies restrict which systems can reach AAA infrastructure such as identity providers, directory services, and authentication servers, reducing the exposure of those services to lateral movement. Identity Firewall (IDFW) extends enforcement by using Active Directory user and group membership directly as the basis for firewall rule decisions. IDFW detects user logins by monitoring login events in domain controller event log servers, then applies security policies based on AD group membership. This allows network access rules to follow user identity across virtual desktops (VDI), Remote Desktop Sessions (RDSH), and physical machines. IDS/IPS profiles can detect attempts to exploit vulnerabilities in authentication services.
+These controls do not replace organizational AAA governance policies or manage AAA solutions across the broader environment. They implement authentication, authorization, and audit mechanisms within the vDefend management layer and provide network-layer protection for AAA infrastructure that supports organizational governance objectives.</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -968,12 +971,9 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) supports least privilege through role-based access control with a defined set of predefined roles and the ability to clone and customize roles for narrower operational scope. The 9.1 release consolidates Site Recovery Manager and vSphere Replication management under a single permissions model where PNR augments vCenter roles and permissions with additional permissions that allow detailed control over PNR-specific tasks and operations. PNR also verifies permissions on the remote vCenter instance as part of its access control validation, so privilege assignments are evaluated at both sites.
-By default, PNR restricts login access to vCenter administrators; other users must be explicitly granted access by an administrator through the PNR interface. Users or user groups assigned a PNR role who are not vCenter administrators do not obtain vSphere Replication privileges, because PNR roles do not include the privileges of vSphere Replication roles. A user who is not a vCenter administrator but requires privileges to perform both PNR and vSphere Replication operations should be added to two user groups, one for each role type, to avoid granting vCenter administrator privileges.
-vSphere Replication uses role-based access control with predefined roles that can be cloned and customized by adding or removing privileges based on organizational needs. PNR supports role propagation to child objects in the inventory hierarchy, allowing administrators to extend privileges from parent objects such as folders to all virtual machines within them, or to assign permissions at specific inventory levels without propagation when narrower scope is required. When permissions are assigned without propagation, users must have at least Read-only permission on all parent objects in the vCenter inventory.
-PNR for VCF Automation access is controlled through role-based permissions assigned to Provider Administrators, Organization Administrators, Project Administrators, and Project Advanced Users, aligning RBAC with VCF Automation tenancy boundaries. Namespace unpair operations require Organization Administrator role authorization. In shared recovery site configurations, PNR restricts users from changing roles or assigning permissions for objects not dedicated to their own use, which helps prevent unauthorized privilege escalation across tenants, and the vCenter administrator manages PNR permissions so that each user has sufficient privileges to configure and use PNR but no user has access to resources belonging to other tenants.
-PNR requires separate privilege assignment for testing a recovery plan and running a recovery plan, which helps prevent unintended changes at both sites that would require significant time and effort to reverse. PNR roles that allow users to run commands on PNR Server should be assigned to trusted administrator-level users only, and PNR server access should be limited to administrators to reduce the number of accounts available to an attacker. PNR administrators can assign SrmAdministrator or SrmProtectionGroupsAdministrator roles to the automatic protection user or user groups for managing automatic protection permissions.
-For the 9.1 Clean Room Orchestrator, at least one user must be assigned the Organization Owner role to enable administrative access to all resources in the Organization, with additional roles available for narrower delegation. VCF Operations orchestrator workflows for PNR require administrator credentials to access and execute, which restricts non-administrative users from performing sensitive recovery operations through the orchestration interface.</t>
+          <t>VCF Protection and Recovery (PNR) implements authenticate, authorize, and audit (AAA) mechanisms for replication and recovery operations. Authentication uses VCF SSO. The PNR server acquires a holder-of-key SAML token from VCF SSO and presents it in a cryptographically signed envelope when establishing authenticated communication channels to remote services such as VMware vCenter. PNR uses service account authentication for server-to-vCenter communication, and a domain-level service account created by vCenter is used when PNR runs in an Enhanced Linked Mode environment. When connecting peer vCenter instances that reside in different or the same SSO domains, PNR also supports credential-based authentication. The PNR Appliance Management Interface requires authentication as the admin user for service management, network configuration, time zone settings, storage replication adapter configuration, and site unregistration workflows. The default admin password is set during initial deployment and is expected to be changed by the operator. PNR exposes Authentication APIs as part of its REST API gateway, including a REST endpoint to log out an authenticated session.
+Authorization is enforced through PNR's privileges, roles, and permissions model. PNR performs operations using the user credentials supplied when the protected and recovery sites are connected, and permission checks apply at both sites for cross-site operations. The configuration import and export tool accepts the --localAuthUseSA and --remoteAuthUseSA parameters, which select whether a Service Account file is used for authentication to the local or remote site. PNR and later supports Service Account authentication for importing or exporting configuration data.
+Audit logging records replication and recovery operations and security-relevant events. PNR records operational information in log files that do not contain private keys or passwords. Authorization errors and certificate verification errors are written with timestamps and component information to security-related log files for audit trail purposes. Replication lifecycle events generate audit log entries, for example the AutoprotectEnabledRpEvent entry that indicates Automatic Protection has been activated for a replication provider.</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
@@ -983,12 +983,11 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides role-based access control mechanisms that scope database and data service access to authorized individuals. DSM defines two roles at the platform level: the Administrator role, which can create, monitor, and manage all data services in the environment; and the User role, which is limited to viewing and managing only the databases and objects the user owns. A user in the DSM User role cannot access data services belonging to other users, and is further restricted to creating and maintaining databases for their own application or designated purpose. Access to database secrets is restricted to the owner of the database, keeping credentials isolated from other users.
-Namespace-scoped role assignments provide an additional layer of access restriction. DSM User role assignments can be limited to one or more specific namespaces, bounding a user's access to only the namespaces to which they have been explicitly assigned. Within a namespace, all assigned users have access to the data services and their secrets scoped to that namespace. DSM namespaces enforce RBAC at the namespace level, supporting collaborative work within a defined group while keeping data services isolated from users in other namespaces. In multi-tenant deployments, DSM administrators assign object stores and data service policies to specific tenants or organizations to maintain tenant isolation across the environment.
-DSM supports mapping directory service groups to specific roles, enabling job-role-based access assignments through an LDAP directory. This allows organizations to align DSM access grants with existing identity stores that reflect job function.
-DSM's Permissions view provides a centralized interface for administrators to create, monitor, and manage user accounts and role assignments. Administrators can modify a user's role and namespace assignments to reflect changes in job function.
-For database provisioning, DSM data service policies include parameter constraints that limit the configuration options available to users. Policy allowlists restrict users to selecting from a specific set of approved parameters, and the "Disallow Custom Database Options" setting fully blocks users from adding database parameters outside the approved set. For SQL Server databases, DSM grants the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access.
-These platform mechanisms operate at the database service layer. Determining which data is sensitive or regulated, identifying which individuals require access based on job role, and translating those organizational decisions into DSM namespace assignments and role configurations is an organizational process outside DSM's scope. DSM provides the technical controls to enforce those decisions once they are made.</t>
+          <t>VMware Data Services Manager (DSM) implements role-based access control natively, with two defined role types that govern access to all data service resources. The DSM Admin role is a super-user role with full access to create, monitor, and manage all data services across the environment. The DSM User role is a restricted role that limits a user to viewing and managing only the data service deployments they own. This separation is enforced at the console level: the views and available actions in the DSM interface differ based on the assigned role, so users with the DSM User role cannot see or act on resources outside their own scope.
+Access control is further refined through namespace scoping. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to data services within those assigned namespaces only. Administrators can modify a user's assigned role and namespace access after initial provisioning. DSM namespaces enforce role-based access control that allows multiple users to work on data services within a shared namespace while maintaining appropriate permission boundaries between them.
+DSM supports both local user accounts and directory service integration for identity management. Local users are created through the DSM UI, where administrators specify the user's role, email address, and password. For enterprise directory integration, DSM supports LDAPS-based authentication with Directory Service Group mapping, allowing administrators to assign users to either the DSM Admin or DSM User role based on their LDAP group membership. This group-based mapping is configured through the vSphere Client during DSM setup or through the DSM UI after deployment.
+Access control extends to storage and database resources as well. DSM IAM policies for S3-compatible storage support granular access control through policy statements that allow specific S3 actions, including PutObject, GetObject, DeleteObject, and ListMultipartUploadParts. At the database level, PostgreSQL instances support the CREATE ROLE command to create database roles for LDAPS users with configurable login capabilities, and administrators can configure Host-Based Authentication (HBA) rules to restrict which clients and authentication methods may connect to a PostgreSQL instance. For SQL Server instances, DSM applies least-privilege access by granting the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access. Data service policies also support allowlist configuration to restrict users to selecting only from a specific set of approved parameters when provisioning databases.
+The DSM Permissions view provides a centralized interface for administrators to create, monitor, and manage configured users. This view supports ongoing governance of who has access to what within the DSM environment, making it straightforward to audit and adjust role assignments as business needs change.</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -998,12 +997,12 @@
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to limiting access to sensitive and regulated data through role-based access control on its administrative control plane, programmable application-layer access policies applied to traffic through its Service Engines, and access controls within the Avi Kubernetes Operator for containerized workloads.
-On the administrative plane, Avi's RBAC system assigns roles with three privilege levels per resource category: Write (full access to create, read, modify, and delete resources), Read (view-only access to configuration, health, and analytics data), and No Access (no visibility to the resource, including inability to read or list it). Roles are scoped through extended granular RBAC using label-based markers, which restrict a user's permissions to specific resources identified by label key-value pairs. Tenant-level label group enforcement, configurable via the enforce_label_group setting, further restricts access to resources tagged with specific label groups. This label-based model extends to cloud objects through the restrict_cloud_read_access field in controller properties. Object-level permissions allow fine-grained separation: Write access to Virtual Services, Application Profiles, SSL/TLS Certificates, and Certificate Management Profile objects can be granted independently of Read-only access to supporting objects such as Health Monitors, Analytics Profiles, PKI Profiles, and Authentication Profiles. Avi documentation recommends creating dedicated roles scoped to SSL/TLS certificate management only and restricting certificate and private key export to the fewest administrators possible.
-Avi Cloud Console enforces its own RBAC layer with Full Access and Read-Only permission levels. Full Access users with the User Administrator or Product Administrator role can manage license and registration functions; Read-Only access limits visibility without modification rights. Within Avi GSLB, non-admin users can be created and assigned roles for granular access control over global load balancing resources.
-On the application traffic plane, DataScript policies allow operators to implement access restrictions at the point where application data flows through the load balancer. DataScript can check client credentials against a String Group configured with key-value pairs and return an HTTP 403 response to any requestor not present in the authorized set, providing whitelist-based access enforcement on virtual services.
-For client traffic logging, Avi's Analytics Profile supports creation of a sensitive log profile that controls how sensitive data is retained and exposed in client logs, reducing the risk that log access broadens exposure of regulated information beyond the intended audience.
-For Kubernetes workloads, the Avi Kubernetes Operator (AKO) Custom Resource Definitions (CRDs) can be secured using Kubernetes RBAC policies, allowing stricter access control over which users can modify load-balancing routing rules for application workloads.</t>
+          <t>VMware Avi Load Balancer (Avi) maintains its own administrative identity plane with mechanisms covering all three AAA elements: authentication, authorization, and audit. User accounts fall into two categories: local users and remote users. Remote users are authenticated through external AAA servers, with support for LDAP, TACACS+, and SAML-based authentication profiles. The product documentation recommends federated authentication as the preferred approach, delegating the authentication process to an organization's central identity provider rather than managing credentials locally within Avi.
+For authorization, the Avi Controller evaluates authorization mapping rules on every user login, updating the user record with tenant and role pairs. Auth Mapping Profiles can map multiple user groups to different roles with tenant isolation, supporting both simple single-role assignments and multi-tenant configurations where a single user requires access across multiple administrative boundaries. The admin user is authorized and responsible for the highest-level configuration operations, including user creation and authorization and tenant management. The admin account is maintained as a locally authenticated account even in a system configured for remote authentication, providing a break-glass path for Controller access.
+The Avi Controller License Hub provides dedicated role-based accounts for administration and auditing. The Admin account holds the enterprise_admin role with full access to deploy and manage security services, perform upgrades, and configure authentication and authorization. The Audit account holds the auditor role with full access to APIs and services for system auditing. LDAP can be configured as an identity provider for License Hub authentication, and the Admin user can reset the Audit user's password.
+Avi also supports OAuth and OpenID Connect (OIDC) for client authentication at the application proxy layer. When configured, the Controller acts as a resource server and retrieves identity information from the OIDC UserInfo endpoint or from ID token claims, enabling per-user identity context to be associated with proxied application traffic. DataScript can check if a user ID is in an approved group list and redirect unauthenticated users to a login page, providing identity-based access control at the virtual service layer.
+In the Avi for VCF Organization-Managed Mode, the organization administrator must be authenticated to edit Service Engine Groups and manage their own infrastructure configurations, reinforcing role-based access enforcement at the VCF integration layer.
+The control asks whether the organization centrally manages AAA across its environment. Avi provides the mechanisms for its own administrative plane and supports integration with a central identity provider, but the organization must configure that integration, maintain the identity provider, and establish processes for reviewing audit log output.</t>
         </is>
       </c>
     </row>
@@ -1035,13 +1034,15 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that contribute to anomalous behavior detection and user activity monitoring, though it does not include a dedicated User &amp; Entity Behavior Analytics (UEBA) or User Activity Monitoring (UAM) solution.
-VCF Operations includes anomaly detection capabilities that use both dynamic and static thresholds to identify when metrics deviate from normal operating behavior. Dynamic thresholding is enabled by default and uses historical data analysis to establish baselines for each monitored object. The Smart Early Warning feature analyzes the number of applicable metrics that violate the dynamic threshold determining normal operating behavior, triggering alerts when the number of anomalies on an object exceeds a trending threshold. When an anomalous entity is detected, VCF Operations generates an outlier violation alert (vmwAnalyticsOutlierEvent, OID 37002), notifying administrators of unexpected behavior. A Critical threshold violation alert is also generated when anomalous entities are detected.
-The Anomalies widget displays detected anomalies for a resource over the past six hours at configurable time intervals, with color-coded criticality indicators. The Anomaly Breakdown widget shows likely root causes for symptoms on a selected resource, helping operators triage issues. The Troubleshooting Workbench includes an Anomalous Metrics card that surfaces metrics exhibiting drastic changes within a selected scope and time window, ranked by degree of change with the most recent anomaly given the highest weighting. Administrators can also examine outlier VMs detected by VCF Operations to identify unexpected behavior and take corrective actions. VCF Operations supports outbound SNMP trap notifications, enabling alert delivery to external SNMP management systems with up to four configurable trap destinations.
-For user activity monitoring, VCF Operations provides a User Activity Audit report that offers traceability of user actions including logging in, operations on clusters and nodes, changes to system passwords, certificate activation, and logging out. Each audit event has a detailed view containing information that supports analysis of events in the virtual infrastructure for suspicious user actions or system issues. Event auditing across the VCF platform provides visibility into platform interaction changes and surfaces suspicious access events and policy violations. Administrators should continuously monitor user security aspects to detect security risks early and respond to potential threats. VCF SSO maintains a dedicated audit log that captures user management events, including account creation, modification, deletion, and activation or deactivation, as well as changes to account credentials and profile information. The vSphere Client's Advanced Export feature allows administrators to export tasks performed by a specific user during a specified time range, providing targeted audit data for investigating suspicious activity.
-Audit logging extends across VCF components. NSX Manager generates audit log messages that record user operations with fields for UserName, ModuleName, Operation, and Operation status, along with detailed resource change information and timestamps. NSX Manager audit logs also record failed login attempts with username and timestamp information, enabling tracking of access patterns across the environment. VCF Operations for Networks captures audit logs of administrative actions, including CRUD operations and login/logout events.
-VCF Operations supports forwarding user activity audit logs to an external syslog server, enabling integration with dedicated SIEM or UEBA platforms for broader correlation and behavioral analysis. VCF Log Management includes content packs that offer pre-built dashboards, alerts, and queries for VCF components. These content packs support security monitoring use cases such as tracking failed login attempts and privilege escalations.
-VCF's built-in anomaly detection is primarily oriented toward infrastructure metrics and operational health rather than user behavior profiling. A dedicated UEBA or UAM solution consuming VCF's audit data would be needed to establish user behavior baselines, detect credential compromise through behavioral deviation, and provide the full scope of analytics this control requires. For organizations requiring deeper behavioral analysis, VMware vDefend extends VCF's monitoring foundation with IDS/IPS, network traffic inspection, and threat intelligence integration.</t>
+          <t>VCF provides layered mechanisms to restrict privileged access to authorized organizational users through centralized authentication, role-based access control, explicit role assignment requirements, and organization-scoped permissions across all platform components.
+VCF SSO and the VCF Identity Broker act as the centralized authentication boundary for the platform. All administrative access to VMware vCenter, NSX, VMware ESX, VCF Operations, VCF Automation, the Supervisor control plane, and VMware Kubernetes Service (VKS) clusters flows through VCF SSO, and administrators control which identity sources are configured. By federating VCF SSO with the organization's enterprise identity provider, access is limited to users who exist in the organization's directory. Users who are not part of a configured identity source cannot authenticate. However, authentication alone is insufficient to gain privileged access. VCF enforces a model where users without explicitly assigned roles cannot access component consoles with their enterprise credentials. An administrator must deliberately assign a role to each user before that user can interact with any VCF component.
+Privileges in vCenter are fine-grained access controls that can be grouped into roles and then mapped to specific users or groups. The AuthorizationManager in vCenter allows or restricts access to specific server objects based on the permissions associated with each object, providing enforcement at the object level. If a predefined role does not match access requirements, administrators can define custom roles containing only the minimum set of required privileges. For example, custom roles can allow users to encrypt but not decrypt virtual machines, so that privileged operations are available only to those with a documented need. vCenter also provides a No Access role that explicitly denies access to a user or group, removing the assigned user's visibility into any objects. This can be applied to non-organizational accounts to remove their visibility and control over the environment.
+Beyond the vSphere Client, the vCenter appliance exposes an Appliance Shell and an Appliance Management Interface, both of which require authentication as root or as a user with the super administrator appliance role. Access to the Bash shell from within the Appliance Shell is disabled by default for non-root users and can be enabled only by a super administrator using the `shell.set --enabled true` command, providing a distinct privileged boundary separate from vCenter's RBAC model.
+Within the Consumption layer, Supervisor Services lifecycle operations require the Manage Supervisor Services privilege on the vCenter system where the service is registered; this applies to adding, activating, and deleting Supervisor Services and to installing the Supervisor Management Proxy. Access to Supervisor and VKS clusters as VCF SSO users requires sufficient role permissions on the relevant vSphere Namespace; the VCF CLI returns a Forbidden error when a user lacks the necessary permissions, providing a clear enforcement signal at the access boundary. vSphere Namespace permissions are assigned to VCF SSO users and groups through three role options: Can View, Can Edit, and Owner. The Owner role is available only with VCF SSO authentication, tying the highest namespace permission level directly to the organizational identity boundary. A VCF SSO user granted the Edit permission on a vSphere Namespace is automatically assigned the cluster-admin role for any VKS cluster deployed in that namespace, making namespace permission grants operations that must be managed carefully to avoid inadvertently elevating external or non-organizational accounts. For organizations connecting VKS clusters to external identity providers, access control can be configured at the provider level to restrict which users within the external organization are permitted to access VKS clusters, adding a pre-authentication gate before Kubernetes role assignments apply. SSH access to Supervisor control plane nodes requires root credentials via vCenter, gating that access behind the organizational identity boundary.
+Inside VKS clusters, Kubernetes RBAC governs what authenticated users can do. The RBAC API restricts privilege escalation by requiring users to hold explicit permissions before they can create or update RoleBinding or ClusterRoleBinding objects; this enforcement is applied at the API level regardless of whether the RBAC authorizer is active. Users cannot grant themselves permissions they do not already possess. Service accounts are subject to the same RBAC framework and should be scoped to the minimum required permissions. The system:masters group should not be used in VKS cluster configurations because membership in that group bypasses all RBAC checks and grants unrestricted super-user access that cannot be revoked through normal RoleBinding or ClusterRoleBinding removal. The privileged Pod Security Admission (PSA) standard, which permits known privilege escalations, should not be used in namespaces serving multi-tenant workloads; namespaces that must allow privileged workloads should establish explicit access controls to restrict who can schedule them. Dynamic Resource Allocation APIs should be controlled through RBAC to restrict access based on user persona. Administrators should apply the least-privilege pattern even for administrative accounts, reserving elevated access for break-glass scenarios. When the requirePasswordOnSudo setting is configured on Supervisor, password entry is required before sudo administrative operations can run, adding an authentication step before privileged commands execute.
+For organizations using VCF Automation, organization-specific roles can be assigned only to users who belong to the organization to which those roles are scoped. This architectural constraint directly restricts non-organizational users from receiving privileged roles within an organization's boundary. Organization users can use only those rights from their roles that are published to their organizations, further limiting privilege scope. Organization administrators can disable users and user groups to immediately deactivate their access and block login. The Organization Owner role can manage users within the organization portal but cannot access services without a separate service role, enforcing separation between user management and operational privileges. The Advanced Rights Bundle Mode allows administrators to control exactly which rights are available to each organization, limiting privilege creep. The accessControls API gives system administrators with the Manage General ACL right programmatic control over access control lists for fine-grained permission management.
+In NSX, users without the Enterprise Administrator role cannot modify or delete protected objects owned by principal identities. Only users with the Enterprise Administrator role can modify or delete these objects, restricting privileged operations on protected configuration to a narrow set of authorized administrators.
+VCF Operations implements role-based access control where users can only perform the actions that their assigned permissions allow. A vCenter user must have either the vCenter Admin role or a specific VCF Operations privilege, such as PowerUser assigned at the root level, to log in to VCF Operations. The administrators role in VCF Operations should be assigned only to specific users who require access to objects and actions across the entire environment.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1051,11 +1052,12 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides network-layer mechanisms that contribute to protecting sensitive and regulated data transmitted to or from external Technology Assets, Applications and/or Services.
-The Distributed Firewall (DFW) and Gateway Firewall (GFW) enforce stateful east-west and north-south policies that restrict which workloads and data flows can reach external services. In VCF multi-tenant environments, Enterprise Administrators can configure Gateway Firewall isolation rules to deny all inter-project communication except designated infrastructure protocols, establishing strict network boundaries for applications that process regulated data.
-TLS Inspection extends this enforcement to encrypted external connections. vDefend External Decryption Action Profiles apply to encrypted traffic destined for external services not owned by the enterprise. Administrators can import or generate trusted and untrusted proxy Certificate Authorities for these profiles. The Crypto Enforcement option controls the permitted protocol versions and cipher suites for client and server connections, allowing administrators to block connections that do not meet minimum acceptable cryptographic standards for data in transit.
-Security Services Platform supports monitoring of application communication paths and segmentation posture. Security Intelligence administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment traffic flows, including flows toward external services. Security Services Platform Application Protection policies can be scoped to cover all application workloads, including critical applications handling regulated data. Security Services Platform guidance recommends restricting or blocking application protocols that transport data in clear text and enforcing minimum secure protocol versions, helping administrators identify and remediate data paths that lack adequate protection before data reaches external services.
-vDefend enforces the network-layer controls through which data protection requirements are implemented but does not govern contractual obligations with third parties, define data classification schemes, or establish the policies specifying which data requires protection.</t>
+          <t>VMware vDefend (vDefend) enforces role-based access control across its security management interfaces to restrict access to firewall policy administration, threat analysis functions, and monitoring capabilities based on assigned user roles.
+The vDefend distributed firewall (DFW) implements RBAC to control who can create or modify firewall rules, limiting policy changes to authorized personnel. Access to DFW monitoring features, including Firewall Insights, requires one of three designated roles: Enterprise Admin, Security Admin, or Security Operator. Rule Analysis operations within the platform are also role-gated across the five defined role types.
+Security Services Platform (SSP) implements RBAC with five defined roles governing access to platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; Full Access grants create, read, update, and delete capabilities, while Read-only access is available for monitoring-oriented roles such as Auditor and Support Bundle Collector. Role assignments can be applied to individual remote users or to remote user groups managed through a directory service, allowing administrators to align vDefend access with existing organizational structures. Multiple roles can be assigned to a single user or group to meet varying operational requirements. SSP's RBAC model also applies to License Hub operations, restricting licensing management actions to authorized roles.
+Security Intelligence RBAC in 9.1 uses the same five-role model as SSP (Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector), aligning Security Intelligence access governance with SSP's permission model and providing consistent role boundaries across both the detection and platform layers.
+For organizations using VCF Automation for vDefend firewall management, VCF Automation provides a dedicated Firewall category under RBAC rights, controlling access to the management and viewing of DFW rules, Tenant Gateway Firewall policy, VPC Gateway Firewall policy, and VPC Security Profiles. This allows organizations to scope firewall administration rights independently of other VCF Automation capabilities, supporting separation of duties between network automation and security policy management.
+vDefend's RBAC controls complement the broader VCF RBAC model by restricting access to network security policy management independently of compute, storage, or platform configuration access. An administrator with VMware vCenter privileges does not automatically gain the ability to modify firewall rules or security analytics configurations unless explicitly granted the appropriate vDefend roles. This separation of duties between infrastructure administration and security policy management supports distinct team structures for network security management.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1065,10 +1067,11 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) contributes to protecting sensitive and regulated data by maintaining replicated copies at geographically separated sites and providing orchestrated recovery when primary copies are compromised or corrupted. Bidirectional protection is implemented by protecting datastore groups or storage policies using array-based replication, or by protecting individual virtual machines using vSphere Replication, allowing organizations to keep regulated workloads recoverable across paired sites.
-Protection groups allow administrators to organize regulated workloads and apply consistent replication and snapshot policies across the virtual machines and datastores subject to the same data protection requirements. PNR protection groups support an immutability mode that, when enabled, prevents the data protection group from being modified or deleted, which addresses tamper resistance for the configuration that governs how regulated workloads are protected. For multi-tenant or shared recovery scenarios, PNR maps resources, networks, folders, and datastores on protected sites to separate datacenters, networks, folders, and placeholder datastores on the shared recovery site, preserving customer data isolation across the recovery boundary.
-vSAN Snapshots and Replication provides VM restore and clone operations from existing snapshots, supporting recovery of regulated workloads to a known-good point in time. PNR records operational information into log files that do not contain sensitive information such as private keys or passwords, which limits the recovery tooling itself as a source of disclosure. The Protection and Recovery dashboards in VCF Operations provide cross-site visibility into protected and recovery sites, vSAN snapshot and replication state, and VMware Live Recovery Cloud regions, supporting monitoring of regulated workload protection.
-Encryption at rest for primary storage, data classification, granular access controls at the data layer, and key management are provided by the underlying VCF platform rather than PNR itself.</t>
+          <t>Protection and Recovery (PNR) implements role-based access control through purpose-built roles registered in VMware vCenter and through a multi-tenant administrative model for Protection and Recovery for VCF Automation. The SRM Administrator role allows users or user groups to perform all PNR configuration and administration operations. The Protection and Recovery Administrator role can be assigned to user groups to manage permissions. Default roles provide the privileges users require to manage protection groups and perform recoveries, while restricting access to resources belonging to other users.
+For automatic protection of virtual machines within a protection group, administrators assign either the SrmAdministrator or SrmProtectionGroupsAdministrator role to the automatic protection user or user group. This scopes the protection actions performed on the user's behalf to the privileges of the assigned role.
+Each role is a collection of privileges that defines the actions a user can perform on the protection and recovery site. A user can have at most one role on an object, but roles combine when the user belongs to multiple groups that all have roles on the object. PNR supports propagating roles to child objects in the inventory hierarchy, so administrators can extend privileges from parent objects such as folders to all virtual machines within them.
+Protection and Recovery for VCF Automation introduces a multi-tenant role model with Provider Administrator, Organization Administrator, Project Administrator, and Project Advanced User. Each role has specific authorization levels for disaster recovery operations. Provider Administrators select which replication classes each Organization can use, restricting organizational access to specific recovery configurations. Organization Administrators manage the pairing of namespaces and assignment of replication classes within their tenancy.
+Underlying directory services, authentication, and enterprise identity governance are provided by VCF SSO and the broader VCF platform. PNR consumes those identities and layers its protection and recovery roles on top of them.</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -1078,12 +1081,11 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to the protection of sensitive and regulated data through several database-platform mechanisms covering data in transit, data retention, storage policy enforcement, tenant isolation, and application-level cryptographic capabilities.
-For data in transit, DSM requires TLS connections to database clusters. Clients establish these connections by adding the relevant certificate authority to the OS trust store, or by retrieving the CA certificate from a custom certificate secret through the DSM API for automated workflows. Beginning with DSM, DSM enforces FIPS 140-3 compliant cryptographic standards and validates certificates during upload, rejecting unsupported algorithms or parameters. A TLS certificate for secure communication between the Consumption Operator and the DSM provider must be obtained and configured by the cloud administrator before enabling self-service consumption.
-For backup and data retention, DSM includes automated backup capabilities with configurable schedules supporting both full and incremental backups. Database administrators configure backup storage locations and retention periods on a per-database basis. DSM retains automated backups of deleted databases until the configured retention period expires, supporting recovery from accidental deletion. Control plane backups are stored in S3-compatible object storage with a unique identifier tied to the control plane ID. DSM supports point-in-time recovery (PITR), restoring a backup at a specified point in time to a newly created database VM. PITR is accessible through both the DSM interface and the VCF Automation UI. If an incremental backup in a backup chain is deleted, DSM cannot restore data from later incremental backups in that chain, so maintaining a consistent backup schedule is important for recoverability.
-For storage placement and access constraints, DSM infrastructure policies control which storage types and storage policies are available for database virtual machines and govern VM placement within the infrastructure. Storage policies in DSM determine the datastore placement of database VMs and filter available storage options to those compatible with the specified compute resource. Data service policies can be defined and enforced across tenants for MySQL, PostgreSQL, and SQL Server databases, including allowlists that restrict users to approved provisioning parameters. In multi-tenant deployments using VCF Automation, administrators can assign object stores and data service policies to specific tenants or organizations, enforcing isolation and resource constraints across database clusters.
-For application-level data protection, PostgreSQL databases in DSM support the pgcrypto extension (version 1.3), which provides cryptographic functions that can be applied to secure specific data fields. DSM also stores its own internal user credentials encrypted using PGCrypto symmetric encryption with a dedicated encryption key. For SQL Server databases, DSM uses an internal management login that restricts user-defined triggers to a database-level security context, blocking access to server-level permissions during management operations.
-Because this control asks whether mechanisms exist to protect sensitive and regulated data wherever it is processed or stored, DSM's contribution is at the database platform tier. The organization remains responsible for classifying what data is sensitive or regulated, configuring database-level access controls that restrict which authenticated users can read or write protected data, selecting storage and backup policies that satisfy encryption and data residency requirements for specific regulated categories, and maintaining a governance program that maps data classification to handling requirements.</t>
+          <t>VMware Data Services Manager (DSM) implements role-based access control natively, with two defined role types that govern access to all data service resources. The DSM Admin role is a super-user role with full access to create, monitor, and manage all data services across the environment. The DSM User role is a restricted role that limits a user to viewing and managing only the data service deployments they own. This separation is enforced at the console level: the views and available actions in the DSM interface differ based on the assigned role, so users with the DSM User role cannot see or act on resources outside their own scope.
+Access control is further refined through namespace scoping. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to data services within those assigned namespaces only. Administrators can modify a user's assigned role and namespace access after initial provisioning. DSM namespaces enforce role-based access control that allows multiple users to work on data services within a shared namespace while maintaining appropriate permission boundaries between them.
+DSM supports both local user accounts and directory service integration for identity management. Local users are created through the DSM UI, where administrators specify the user's role, email address, and password. For enterprise directory integration, DSM supports LDAPS-based authentication with Directory Service Group mapping, allowing administrators to assign users to either the DSM Admin or DSM User role based on their LDAP group membership. This group-based mapping is configured through the vSphere Client during DSM setup or through the DSM UI after deployment.
+Access control extends to storage and database resources as well. DSM IAM policies for S3-compatible storage support granular access control through policy statements that allow specific S3 actions, including PutObject, GetObject, DeleteObject, and ListMultipartUploadParts. At the database level, PostgreSQL instances support the CREATE ROLE command to create database roles for LDAPS users with configurable login capabilities, and administrators can configure Host-Based Authentication (HBA) rules to restrict which clients and authentication methods may connect to a PostgreSQL instance. For SQL Server instances, DSM applies least-privilege access by granting the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access. Data service policies also support allowlist configuration to restrict users to selecting only from a specific set of approved parameters when provisioning databases.
+The DSM Permissions view provides a centralized interface for administrators to create, monitor, and manage configured users. This view supports ongoing governance of who has access to what within the DSM environment, making it straightforward to audit and adjust role assignments as business needs change.</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -1093,10 +1095,14 @@
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides geographic enforcement mechanisms at the application delivery layer that help organizations restrict application traffic flows by source geography. The Geo-DB feature allows administrators to define named groups of geographic entities, including specific country lists and regional groupings such as embargo country sets, which can then be applied as match conditions in virtual service traffic policies. This allows Avi to block, log, or redirect requests based on the geographic origin of the connection.
-The Avi Web Application Firewall (WAF), built on the ModSecurity rules engine, extends geographic enforcement through the t:IPtoCountryCode transformation. This transformation converts a client IP address to its corresponding country code within WAF rule expressions, enabling administrators to write rules that match and act on traffic associated with specific jurisdictions. Geo-DB policy groups and WAF country-code rules can be layered to create enforcement at the application proxy boundary.
-The Avi Analytics Profile supports configuration of a sensitive log profile that controls how sensitive data appearing in client logs is handled. This limits inadvertent exposure of regulated data within Avi's own telemetry and complements the traffic enforcement mechanisms described above.
-Effective use requires that the organization identify which applications process data subject to cross-border transfer regulations, determine which jurisdictions are restricted or permitted, and then configure the corresponding Geo-DB groups and WAF rules. Avi provides the enforcement mechanism; the underlying data classification and jurisdictional analysis are organizational responsibilities.</t>
+          <t>VMware Avi Load Balancer provides a native, multi-tiered Role-Based Access Control (RBAC) framework that governs all administrative access to the Avi Controller. At the base level, Avi roles assign one of four privilege types to each resource category: Write (full create, read, modify, and delete access), Read (view-only access to configuration, health, and analytics data without modification capability), Assorted (a mixed access level combining permissions across specific operations), and No Access (no access to the resource at all, including the inability to read or list it). Roles are combined with tenants to define the complete authorization settings for each user, scoping what resources a user can interact with and what actions they may take.
+Beyond base privilege levels, the Extended Granular RBAC feature refines access using markers, which are key-value label pairs assigned to Avi objects. A role definition specifies that a user may access only objects bearing labels that match the role's marker set. The allow_unlabelled_access parameter controls whether a user can view objects that lack matching labels, allowing administrators to restrict visibility to labeled objects only. Label groups can be associated with tenants to enforce label-based access policies across the tenant boundary. Multiple label values can be mapped to a single key, enabling flexible classification schemes. This mechanism enables resource-level scoping across tenants and teams: for example, restricting a group of operators to only the virtual services labeled with their team's identifier, without granting visibility into other teams' objects.
+At the finest granularity, Avi implements sub-resource (field-level) RBAC, which scopes which specific fields within a configuration object a given user is authorized to modify. Sub-resource definitions can be combined so that a user can configure multiple fields or features within a single object while remaining restricted from updating others. Label-based permissions for cloud objects extend this field-level control to infrastructure resources managed by the Avi Controller. Virtual service configuration exposes RBAC directly: the RBAC tab in the Virtual Service advanced setup provides label-based access control for health monitors and associated objects, extending role enforcement down to individual service configuration items.
+For GSLB deployments, the Avi Controller enforces RBAC through role references such as Gslb_Group_Enabled and Gslb_Health_Monitor that can be assigned to user accounts with tenant-level scope. These role references apply to follower sites configured with federated JWT profiles, scoping which accounts can modify GSLB configuration.
+The Avi Controller applies RBAC within the License Hub, limiting which users can perform specific actions based on their assigned role.
+For deployments using the Avi Kubernetes Operator (AKO), the Avi Controller implements RBAC by assigning tenants and roles to user accounts at the Kubernetes or OpenShift cluster level. AKO Custom Resource Definitions (CRDs) can leverage Kubernetes RBAC policies to restrict which user groups can configure routing rules, extending the Controller's authorization model into the Kubernetes control plane.
+For deployments on Microsoft Azure, Avi integrates with Azure IAM to control which Azure identities have access to Avi Load Balancer resources hosted in Azure. Administrators can use built-in Azure roles such as Reader (read-only access) or Owner (full access), or define custom roles for finer control over specific resources.
+RBAC configuration is managed through the Users section of the Avi Controller UI. Roles are defined per resource type and then assigned to users within a tenant. Extended Granular RBAC markers are attached to individual Avi objects (virtual services, pools, health monitors, and others) and referenced in the role definition. Sub-resource RBAC is configured as part of the Extended Granular RBAC object, combining field-level restrictions as needed.</t>
         </is>
       </c>
     </row>
@@ -1128,13 +1134,17 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to IT Asset Management programs through built-in inventory, discovery, and integration capabilities that provide the technical foundation for asset tracking and governance.
-VCF Operations groups discovered objects logically and provides detailed inventory lists across the environment, covering compute, storage, and networking resources. The inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group.
-The Service Discovery adapter automatically discovers applications, services, and their associated metrics (CPU, memory) running on managed infrastructure. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be exported in CSV format for use in external asset tracking systems.
-For organizations using ServiceNow, VCF provides two integration paths. The Management Pack for ServiceNow in VCF Operations populates the ServiceNow CMDB with discovered resources through the ServiceNow Table API and CMDB Meta API, providing CMDB visibility within VCF Operations. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation provides a structured data source that captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-VCF Automation adds governance through its project model, which controls who can deploy what resources and where those resources are deployed. Projects link users, catalog items, and IaaS resources together. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources.
-Tags within VCF Automation express capabilities and constraints that define deployments. Cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-The broader ITAM program responsibilities of establishing asset governance policies, defining ownership lifecycles, and maintaining organizational accountability remain outside VCF's scope.</t>
+          <t>VCF provides several foundational capabilities that support a Zero Trust Architecture approach, though a complete ZTA implementation requires organizational policies, identity governance processes, continuous verification mechanisms, and additional tooling beyond what VCF delivers on its own.
+VCF enforces authentication as a prerequisite to all access. The platform's authentication framework determines whether users are who they claim to be through credentials including smart cards, usernames, and passwords. VCF SSO integrates with the VCF Identity Broker to provide centralized authentication for VCF components, with support for identity provider federation to enterprise directories such as Active Directory Federation Services. Federating vCenter to an enterprise identity provider provides flexible options such as multi-factor authentication. OAuth 2.0 support allows information exchange among web services without exposing sensitive data such as usernames and passwords, reducing credential exposure during authentication flows. NSX network devices require authentication prior to establishing any management connection for administrative access, and all administrative accounts must be password protected. VMware ESX and vCenter systems restrict connections to authenticated users and they can access only those objects for which they have the required privileges and are authorized to use or view. Direct access to the ESX host console can be restricted to prevent administrators from overriding policy enforcement, and ESX supports configuration of users who can override lockdown mode and access the DCUI. For Windows virtual machines, vSphere Virtualization-based Security supports Credential Guard, which isolates and hardens key system and user secrets in the guest operating system against compromise. At the workload consumption layer, VMware Kubernetes Service (VKS) clusters support multiple authentication mechanisms for the Kubernetes API server, including OIDC federation with VCF SSO, X.509 client certificates, service account tokens, and webhook token authentication. Namespace-level access in VKS follows the same VCF SSO identity model as the broader vSphere platform. VKS implements a zero-trust token validation posture for external integrations such as AWS IRSA, trusting tokens only when issuer, signature, audience, and subject conditions are verified. Kubernetes guidance recommends enabling as few authentication mechanisms as necessary to simplify user management and prevent retained access through unused pathways, and it recommends setting short certificate lifetimes with automated rotation to limit the window of opportunity for credential misuse.
+Once authenticated, VCF applies authorization controls that restrict what each principal can do. The vCenter AuthorizationManager controls access to specific server objects based on the permissions associated with each object. Authenticated users can view objects or invoke operations on the server only when the permissions associated with their account allow it. Administrators can create, modify, and manage roles and permissions through the AuthorizationManager, enabling granular role-based access control across the vSphere environment. The CloudAdmin role restricts access to platform-level operations, and the No Cryptography Administrator system role supports all Administrator privileges except for Cryptographic Operations privileges, allowing organizations to separate encryption key management from general administration. You can clone the No Cryptography Administrator role and create custom roles with only some of the Cryptographic Operations privileges to further limit what users can do. NSX provides granular role separation within the VPC scope, where you can assign VPC Admin, Network Admin, Security Admin, Network Operator, and Security Operator roles. A VPC Admin has full access to all networking and security objects inside an NSX VPC, while other roles provide narrower access. This "authenticate first, then authorize" model aligns with core ZTA principles of never granting implicit trust. For containerized workloads, Kubernetes RBAC provides Role, ClusterRole, RoleBinding, and ClusterRoleBinding objects that define what each authenticated identity may perform at the namespace or cluster level. Least-privileged access applies even to administrators; elevated access is reserved for break-glass scenarios while standard operations use narrower roles. Authorization webhooks support fine-grained, attribute-based authorization decisions by passing field and label selector information to the webhook, enabling per-resource access control based on object attributes such as node name and labels. Dynamic Resource Allocation APIs carry elevated privilege implications and should be controlled using RBAC to restrict access based on user persona. Pod Security Admission enforces workload security profiles at the namespace level, with Baseline and Restricted profiles limiting privilege escalation, host namespace access, and container capabilities. Security contexts allow administrators to require that containers run as non-root users, drop Linux capabilities, apply seccomp profiles, or use AppArmor to restrict system call access at runtime. Cluster administrators can create custom pod security policies beyond the platform defaults and bind them to specific users, applying different trust levels to different teams or namespaces. Argo CD, available as a standard package for VKS clusters, supports local account authentication backed by global RBAC policies that define access control through policy rules and group mappings, extending authenticated and authorized access controls to the continuous delivery pipeline. Harbor, also deployable as a VKS standard package, enforces role-based access control for artifact management, requiring authentication and authorization before users can pull or push container images and charts.
+Solution-to-solution communication within VCF uses certificate-based trust rather than passwords. VCF Automation establishes trust relationships with servers by verifying and trusting certificate information for SSL communication. When a client receives an element from VCF Operations, it verifies the server identity and decides whether to trust the signature before proceeding. Mutual TLS authentication based on self-signed or CA certificates is required between hosts and the NSX Central Control Plane. The VCF Identity Broker provides a centralized authentication source for VCF components, and vCenter and NSX components connect to it for SSO-based access. This certificate-based trust model means that VCF's own internal communications follow a verify-then-trust pattern rather than assuming trust based on network location. At the consumption layer, the Secret Store Supervisor Service enforces RBAC for administrators, DevOps engineers, and application tenants managing and distributing sensitive data, providing controlled access to credentials without broad exposure. Kubernetes guidance recommends using short-lived secrets to limit the impact of unintentional credential exposure, and audit rules can alert on anomalous access patterns such as concurrent reading of multiple secrets by a single user. Scoping IAM role trust policies to specific service accounts and namespaces enforces least-privilege at the credential level within VKS deployments.
+VCF's networking layer provides segmentation capabilities that support ZTA network isolation. NSX projects enable multi-tenancy by isolating security and networking objects across tenants within a single NSX deployment, so that each tenant's resources are separated from others. NSX VPC enables tenant-level isolation of both networking and security objects, with each VPC operating as a self-contained boundary. Security groups can further define isolation settings for on-demand private or outbound networks. Kubernetes network policies can be imported to NSX and converted to vDefend policies, extending consistent security boundaries to containerized workloads alongside traditional VMs. The vSphere Distributed Services Engine supports zero-trust security by offloading network security processing to a dedicated data processing unit, separating security enforcement from the host operating system. These segmentation capabilities allow organizations to build network architectures where lateral movement between zones requires explicit authorization. VMware vDefend extends this foundation with microsegmentation and identity-based firewall rules that integrate with Active Directory for user-aware access enforcement at the workload level. At the Kubernetes networking layer, Cilium, a supported CNI option, enforces network policies at layers three through seven using an identity-based security model that is decoupled from network addressing, allowing policy to follow workload identity rather than IP addresses. Istio's ambient data plane mode, available as a standard package for VKS clusters, uses a per-node ztunnel component to provide mutual authentication and encrypted transport for east-west traffic within the mesh, extending verify-before-trust semantics to workload-to-workload communication. Service meshes operating at layer seven can enforce policies based on workload identity and frequently provide mutual TLS to maintain data confidentiality even in the presence of a compromised node.
+VCF Operations provides visibility into platform activities through audit event collection. VCF Operations reports on authentication and security-related audit events, and each audit event has a detailed view containing information that helps analyze events in the virtual infrastructure for suspicious user actions or system issues. This supports the continuous monitoring aspect of zero trust by correlating authentication events, configuration changes, and related activity across the environment.
+To realize a full Zero Trust Architecture, organizations need to supplement VCF's technical controls with an overarching ZTA policy framework that defines trust boundaries, continuous verification requirements, and least-privilege access principles across all systems. Device posture assessment, continuous session monitoring, and adaptive access policies based on risk signals typically require integration with identity governance platforms and security analytics tools beyond what VCF provides natively.
+Zero Trust Architecture requires that every user and device be authenticated and authorized before accessing data or resources, with no implicit trust based on network location or prior access. VMware Private AI Services (PAIS) implements authentication and access control mechanisms across its AI services layer that support this model.
+PAIS enforces access through OIDC-based group membership. The PAISConfiguration custom resource requires an issuer URL, a client ID, and scopes including openid, groups, and offline_access, with a groups claim carried in the access token. Access is restricted to user accounts that belong to authorized groups configured via the authorizedGroups setting, and users outside those groups are denied access regardless of network position. Communication with the OIDC provider is required over HTTPS, and an issuer certificate must be present for that provider. PAIS supports a single OIDC provider per configuration.
+Certificate-based mutual trust is enforced across PAIS component connections. CA trust bundles are required for the OIDC provider, the Harbor registry hosting the model gallery, content management systems used as data sources in Data Indexing and Retrieval, MCP servers providing tools to models, and the pgvector database server storing vector embeddings for Knowledge Bases. Trust bundles are configured through VCF Automation by uploading a certificate file or referencing a ConfigMap in the namespace, and the worker.clientTls.caBundleRefs setting controls the CA bundle references used for client TLS connections. Separate trust bundles per application are recommended, with refreshes required before certificate expiration.
+At the model and data plane, the Model Gallery uses Harbor project access controls to restrict access to sensitive model training and tuning data, and model endpoints authenticate to private registries through a harbor-pull-secret-readonly secret. Remote MCP servers connected to PAIS can use static authentication tokens, and Knowledge Base data sources such as Confluence and SharePoint require a user name and password or a personal access token configured per administrator settings. Grafana dashboards visualizing PAIS metrics also authenticate through the OIDC provider, extending OIDC-mediated access into the observability path.</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1144,13 +1154,10 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to secure baseline configurations within its network security domain by providing structured configuration management capabilities, predefined security profiles and strategies, and configuration integrity controls that align with industry-accepted hardening practices.
-vDefend supports draft configuration management with configuration locking to prevent multiple users from simultaneously opening and editing a manual draft, helping maintain configuration integrity and reducing the risk of conflicting changes to firewall policy. Role-Based Access Control (RBAC) in vDefend governs who can create or modify firewall policies, providing control over which administrators can alter the security baseline.
-In vDefend, five system-defined VPC Security Strategies are available for establishing security baselines across Virtual Private Clouds (VPCs): VPC Isolation, VPC Isolation with Essential Services, VPC External Connectivity, VPC Secure Connection, and NONE. These strategies are consumed through Security Profiles in VCF Automation, which are predefined configuration templates that define the default security posture for VPCs. VPC Security Strategies provide a declarative, consistent way to apply DFW security baselines across multiple VPCs within a project, and Project Admins are guided to select a pre-defined high-level security posture that enforces Secure by Default principles rather than manually configuring individual firewall rules. Security profiles can be applied to one or more VPCs simultaneously and updated as requirements evolve.
-vDefend provides predefined TLS Decryption Action Profiles with four settings: Balanced (default), High Fidelity, High Security, and Custom. These profiles are vendor-defined baseline configurations for TLS inspection behavior, giving organizations a documented starting point aligned with different security postures. TLS Inspection policies also support an Advanced Configuration option to lock policies, preventing multiple users from making concurrent changes to TLS inspection policy baseline settings.
-Security Services Platform validates configuration changes before implementation through a deployment wizard that conducts thorough validations to confirm configurations are correct and compatible. The platform enforces initial security policies that cannot be modified through the user interface after they have been published, providing an immutability mechanism for foundational policy baseline elements. Security Services Platform supports backup and restore of configuration data, and certificate consistency between backup and restored environments should be verified to maintain NDR sensor integrity.
-Security Services Platform's Bare Metal Security feature extends vDefend policy enforcement to physical servers, applying L3/4 security policies to bare metal infrastructure using the same policy model and management plane as virtualized workloads. Two default DFW rules are created when Bare Metal servers are onboarded to Security Services Platform, providing an immediate baseline posture for physical infrastructure. Security policies are defined, propagated, and enforced across Bare Metal servers with consistent application and monitoring.
-vDefend's configuration management capabilities operate within the network security layer. The broader secure baseline configuration program for VCF, including the VCF Security Baseline document, component hardening guides, DISA STIGs, and compliance scanning through VCF Operations, is managed at the platform level. vDefend contributes by maintaining its own secure defaults and configuration controls within the network security domain.</t>
+          <t>VMware vDefend (vDefend) is a foundational technology for implementing Zero Trust Architecture (ZTA) within VCF. While a full ZTA implementation also requires identity governance, organizational policy, and continuous verification processes beyond any single product, vDefend provides the network security enforcement layer that treats all east-west traffic as untrusted by default and enforces explicit authorization at the workload level.
+vDefend enforces security policies at the vNIC level, meaning every virtual machine's network interface is individually firewalled regardless of its network location. Network location does not confer trust, and every communication must be explicitly permitted. The default-deny posture of Distributed Firewall rules means workloads cannot communicate unless a policy explicitly allows that traffic, reducing the risk of lateral movement by treating all internal traffic as untrusted. The Distributed Firewall Connectivity Strategy feature simplifies micro-segmentation rule creation for applications, lowering the operational barrier to deploying a Zero Trust model.
+Security Services Platform provides a guided security segmentation journey that walks administrators through a staged implementation of zero trust using vDefend. This workflow moves from broad infrastructure segmentation through environment-level isolation to fine-grained application ringfencing, where policies are defined down to the individual application tier. Security Intelligence complements this journey by providing the visibility and analytics needed to understand application security policy requirements, supporting identification of gaps in the zero trust posture. Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and network flows to support Zero Trust journey planning. Security Services Platform also enforces role-based access control by assigning platform roles to remote users and user groups, subjecting access to the security management plane to the same authorization principles that govern workload-level policies.
+vDefend Identity Firewall extends the zero trust model beyond IP-based rules by integrating with Active Directory to create firewall rules based on user identity and group membership. Administrators can define policies that grant or restrict access based on authenticated user identity rather than IP address. Identity Firewall rules can specify source users or groups, destination resources, services, and context profiles to allow or deny traffic based on user identity. Identity Firewall also supports simultaneous logins by multiple users on the same virtual machine, with each user's application access controlled based on their role requirements. Administrators can use Identity Firewall with Remote Desktop Session Host to create Active Directory security groups that allow or deny users access to application servers based on their assigned role. Identity Firewall supports two login detection methods: Event Log Scraper (ELS), which reads Windows security event logs from domain controllers, and Guest Introspection, which captures authentication events from within the guest operating system. The choice between these methods depends on the workload type and deployment environment.</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1159,112 +1166,6 @@
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable security baseline mechanisms for its replication and recovery infrastructure. The PNR appliance includes a security reference section that identifies configuration files containing settings that affect environment security, and PNR documentation establishes that secure operation depends on proper configuration and maintenance of the PNR server. The security reference also documents network port requirements, providing the technical specifications needed to develop and maintain secure baseline configurations for disaster recovery infrastructure.
-PNR includes a Configuration Import/Export Tool that captures the complete set of protection and recovery configuration settings, including server version, build number, local and remote site names, inventory mappings, placeholder datastores, advanced settings, and array managers. The tool supports both UI-based and scripted exports and can transfer configuration data without requiring credential entry when using the bundled generated script. This gives organizations a mechanism to document, back up, and restore known-good baseline configurations for their disaster recovery infrastructure. The underlying system configuration is stored in the va-configurator.xml file and is accessible through Advanced Settings on the Site Pair tab in the management interface, providing a defined location for baseline review and modification.
-The PNR appliance management interface allows administrators to configure appliance security settings after deployment. The Advanced Settings system provides privileged users with the ability to adjust default values governing protection and recovery features. When modifying the minimum protocol version for TLS, PNR requires that the change be applied consistently across all configuration occurrences in the system, supporting systematic baseline management for transport security settings.
-For cyber recovery deployments, PNR documentation recommends using standard VCF topology with separate workload and management domains to achieve better isolation and align with security best practices at the recovery site.
-Full compliance with this control requires an organizational baseline configuration management program, documentation practices, version control, and hardening tooling extending beyond what PNR provides directly.</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) contributes to secure baseline configuration management through its infrastructure policy framework, data service policy enforcement, and built-in secure defaults for authentication and certificate management.
-Infrastructure policies in DSM define the compute, storage, and networking resources for each database deployment, including the list of allowed VM classes and compatible storage policies. These policies are configured by DSM administrators and act as standardized, repeatable deployment baselines that database users must follow. When administrators configure infrastructure policies, they constrain the quality and quantity of resources that users can consume from vSphere clusters, establishing guardrails that support consistent deployments across the environment. Database cluster creation applies both infrastructure policies and storage policies that enforce isolation and resource constraints, reducing the risk of misconfiguration by individual users.
-Data service policies extend this baseline enforcement across multi-tenant deployments. DSM administrators can define and configure data service policies for various database services and enforce them across different tenants to maintain a consistent security and compliance posture. Data service policies constrain which infrastructure options can be applied to database instances. When DSM is integrated with VCF Automation, data service policies can be applied consistently across organizational units.
-DSM also ships with predefined secure defaults for database authentication. PostgreSQL databases on DSM use scram-sha-256 as the default password-based authentication method, as configured in the default pg_hba.conf entries stored at /pgsql/data/pg_hba.conf. Custom pg_hba.conf entries support scram-sha-256, reject, and cert authentication methods. TLS is enforced by default for database client connections, with an administrator-controlled option to relax enforcement via the postgrescluster-allow-non-ssl-system-users setting in the advanced-system-config ConfigMap within the dsm-system namespace.
-Certificate management is integrated into the database creation workflow and validates certificate chains for connections to external systems, including VMware vCenter. DSM introduces a stricter default certificate validation mode, the "latest" mode, that enforces cryptographic and KeyUsage validations for all DSM endpoints, including the Provider VM and data service clusters. Certificates uploaded to DSM are validated against FIPS 140-3 cryptographic standards, and uploads containing unsupported algorithms or parameters are rejected. Custom trusted root certificates must comply with FIPS requirements. DSM also verifies the SHA256 thumbprint of vCenter during initial configuration to confirm the management connection targets the expected endpoint. Custom certificate support allows organizations to replace the default DSM certificate with organization-issued certificates for both the Provider VM and database clusters. For self-service deployments using the DSM Consumption Operator, signature verification confirms package integrity before installation.
-DSM validates certificate chains using configured root CA certificates stored in ConfigMaps and supports private container registry configuration with CA certificate validation for air-gapped environments.
-Addressing this control fully requires organizational processes beyond what DSM provides directly. DSM does not include tooling to document baseline configurations in a compliance-ready format, map configurations to specific industry hardening standards, or audit deviations from defined baselines over time. Organizations should supplement DSM's policy and defaults framework with configuration management documentation, change tracking processes, and integration with compliance scanning tools to satisfy the full requirements of this control.</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) provides several built-in mechanisms that support the development and application of secure baseline configurations for the application delivery layer.
-The SSL/TLS Profile system gives administrators a documented starting point for cryptographic configuration. Profile Templates define accepted SSL and TLS versions and ciphers in prioritized order, and can be associated with virtual services or the Controller itself. The Standard SSL/TLS Profile is suitable for typical deployments, while the System-Standard profile provides modern cipher suites for backend server re-encryption in Kubernetes environments managed through the Avi Kubernetes Operator (AKO). Avi includes a curated list of cipher suites considered reasonably strong for SSL/TLS configuration, and the documentation notes the trade-offs between security, compatibility, and computational expense when selecting profiles. The Service Engine disables unsafe legacy renegotiation by default, providing a built-in protocol hardening baseline that reduces the risk of protocol downgrade attacks.
-The System-Secure-HTTP application profile is a pre-configured baseline for securing HTTP virtual services. It enforces HTTPS, protects cookies, manages client IP handling, and controls protocol behavior, giving administrators a hardened starting point for web application delivery. Administrators can supplement these defaults with more granular settings through policies or DataScripts.
-For deployments requiring validated cryptographic modules, Avi Load Balancer implements FIPS 140-3 compliance, providing a cryptographic baseline aligned with the U.S. and Canadian government standard for cryptographic modules.
-The Avi Web Application Firewall (WAF) Positive Security model supports application-layer baseline configuration through rules that define allowed application behavior. Each rule supports Enable/Disable control, mode selection between Detection and Enforcement, and configurable Paranoia levels, allowing organizations to tune an application security baseline to their risk posture. The Positive Security Rule Updates feature can be enabled to activate additional configuration options for application security policies. The Cloud Console Application Rules service extends this with rules specifically designed to address known application vulnerabilities, including those with CVEs, and updates them automatically.
-For Kubernetes deployments, AKO uses Custom Resource Definitions (CRDs) to enable syntactical validation of configuration objects at creation time, which helps prevent invalid configurations from being deployed. The AKO L4 CRD Rule supports SSL profiles and PKI profiles for securing pool connections, allowing Kubernetes-native expression of Avi's cryptographic baseline settings.
-Certificate lifecycle management supports maintaining cryptographic baselines over time. Certificate Management Profiles support automated certificate renewal workflows, and the Trust Protection Platform integration can automatically handle certificate and chain certificate renewals by learning the mapping of virtual service names to their certificates.
-The organizational process of developing, documenting, and maintaining baseline configurations across all in-scope technology assets, including selecting appropriate profile settings, applying them consistently, and updating them as software versions and security guidance evolve, remains outside what Avi performs on the organization's behalf.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Tenet 6</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>AST-02.2, AST-02.5, AST-02.9, IAC-01, IAC-01.2, IAC-06, MON-01, NET-01.1</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>All resource authentication and authorization are dynamic and strictly enforced before access is allowed. This is a constant cycle of obtaining access, scanning and assessing threats, adapting, and continually reevaluating trust in ongoing communication. An enterprise implementing a ZTA would be expected to have Identity, Credential, and Access Management (ICAM) and asset management systems in place. This includes the use of multifactor authentication (MFA) for access to some or all enterprise resources. Continual monitoring with possible reauthentication and reauthorization occurs throughout user transactions, as defined and enforced by policy (e.g., time-based, new resource requested, resource modification, anomalous subject activity detected) that strives to achieve a balance of security, availability, usability, and cost-efficiency.</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a layered identity and access management architecture spanning centralized identity services, role-based access control, group-based access policies, identity provider federation, and programmatic access management through APIs.
-VCF SSO is the centralized authentication service. VCF SSO issues security tokens that grant authenticated users access to VMware vCenter, NSX Manager, VCF Operations, and other platform components without requiring separate credentials for each service. VCF Operations supports importing users and groups from VCF SSO for consistent identity management across the stack. VMware Identity Manager provides a platform for managing users and groups, managing resources and user authentication, and configuring access policies and resource entitlements. vCenter also supports built-in identity source authentication using local domain credentials. The built-in identity provider can also be configured to use Active Directory as an identity source through LDAP/S, OpenLDAP/S, or Integrated Windows Authentication (IWA), depending on the directory environment.
-VCF supports federation with enterprise identity providers. vCenter can be federated to providers such as Microsoft Entra ID, ADFS, and Okta, which enables multifactor authentication and automatic user synchronization with the organization's directory. PingFederate is also supported as a federated identity provider; for these integrations, vCenter uses System for Cross-domain Identity Management (SCIM) to automate the exchange of user and group identity information between the external identity domain and vCenter. VMware Identity Broker allows principals to authenticate to vCenter through an external identity provider. NSX Manager can be configured to authenticate users from identity management providers and can be integrated with Workspace ONE Access for identity management services. The Supervisor component supports registration of OIDC-compliant external identity providers for authentication to VMware Kubernetes Service (VKS) clusters; supported providers include Okta, Workspace ONE Access, and Dex, configured by supplying the Supervisor callback URL to the identity provider.
-Role-based access control is enforced across all VCF components. In vCenter, permissions associate a user or group with a role on a specific inventory object, and predefined roles cover common administrative functions. Custom roles can be created with only the minimum required privileges for a given workflow. Managing identity provider configuration in vCenter requires the VcIdentityProviders Manage privilege. VCF Operations supports group-based access control, allowing administrators to configure groups and assign roles that control access to dashboards, reports, policies, alerts, and administration functions, as well as granular role-based controls for platform operations including approvals, audits, certificates, and content libraries.
-VCF Automation extends access management through organization-level and project-level controls. The VCF Automation Access Control service supports identity operations for managing groups and users, including editing user names, passwords, and role assignments. The organization portal enforces role-based access control, requiring either Organization Administrator or Organization Auditor roles to manage policy templates. Organization administrators can distribute infrastructure and configure group-level access through the organization management functionality. Project access is governed by predefined roles. Users and groups can be disabled at the organization level to revoke access without deleting accounts. The System Administrator role has the right to manage and view Access Control Lists, and the accessControls API allows administrators to view and manage ACL entries for defined entities.
-For Kubernetes workloads within the VCF consumption layer, VKS supports two authentication methods: VCF SSO and OIDC-compliant external identity providers. The OIDC path is implemented through Pinniped and supports providers including Okta, Workspace ONE Access, Dex, GitLab, and Google OAuth. Configuring an external provider requires setting up an OpenID Connect ID Token with a Groups claim type filter to enable group-based access control tied to the organization's directory. Custom ClusterClass configurations allow clusters to authenticate developers using existing corporate identity systems. VKS supports namespace permission roles: Owner (full control including deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). These roles map to Kubernetes ClusterRoles through RoleBindings, and RoleBinding objects can reference VCF SSO users and groups directly to integrate SSO identities with Kubernetes role-based access control. A user with the Namespaces.Edit privilege on a user-created Namespace folder can perform CRUD operations on Kubernetes API resources in the Supervisor. Namespace Self-Service permissions control which users can self-provision namespaces through kubectl.
-Kubernetes RBAC is the primary authorization mechanism within VKS, using Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings to bind permissions to users, groups, or service accounts. Kubernetes Attribute-Based Access Control (ABAC) is also available, defining access rights through policies that combine user, namespace, resource, and access mode attributes. Authorization webhooks can interpret field and label selectors to enforce fine-grained access control based on resource attributes such as node names and labels.
-Service accounts provide namespaced workload identity within VKS clusters. For Windows containers, the Group Managed Service Account (gMSA) Webhook allows containers to run as Active Directory identities. VKS service accounts can be annotated with IAM role ARNs to enable pod identity and role assumption for cloud resource access through OIDC federation, replacing long-lived static credentials with short-lived, least-privileged credentials on demand. IAM role trust policies can be scoped to specific service accounts and namespaces to enforce least privilege.
-Several supplementary services within the VKS layer extend the IAM surface. Harbor Registry, available as a standard package on VKS clusters, enforces role-based access control to manage access to container image artifacts. The Secret Store Supervisor Service enforces RBAC for administrators, DevOps engineers, and application tenants managing sensitive data. Argo CD supports both OIDC configuration for external identity providers and local account configuration with global RBAC policies that define role-based access through policy rules and group mappings. The Istio service mesh package includes a pluggable policy layer supporting access controls, rate limits, and quotas at the service-to-service level.
-Programmatic access management is available through several APIs. The Identity API authenticates and manages the authorization provider. The Identity Service and Infrastructure as a Service APIs are used to acquire access tokens for REST API authentication. Principal Identity users authenticate using client certificates for service-to-service communications between VCF components.
-NSX integrates with LDAP and external identity management services for administrative access to networking configuration. NSX Manager enforces role-based access control with roles such as auditor and network administrator assignable to LDAP users. vDefend, a separate product that extends NSX with security capabilities, offers an Identity Firewall that integrates with Active Directory for identity-based firewall rules.
-VMware Private AI Services (PAIS) provides OIDC-based authentication and group-based authorization for AI workloads, the primary IAM mechanisms controlling access to model endpoints, the model runtime, Agent Builder, and Data Indexing and Retrieval capabilities. PAIS authentication is configured with an issuer URL, a client ID (pais-authentication-id), and the openid, groups, and offline_access scopes. The OIDC provider must support the .well-known/openid-configuration discovery endpoint. Authorization restricts access to user accounts that are members of named groups listed in the authorizedGroups setting (such as group-for-pais-access-01 or group-for-pais-access-02). A groups claim is included in the Access Token and a corresponding groups scope is created in the OIDC configuration, while the oidc-groups-claim setting selects which claim name carries group membership when the OIDC provider uses a non-default name. The oidc-extra-audiences setting accepts additional OAuth 2.0 client identifiers that PAIS will accept when validating Access Tokens, supporting integration with downstream clients that present their own audience. Activating PAIS in an organization namespace requires coordination with the OIDC provider administrator and an organization administrator account in VCF Automation.
-Identity provider integration for PAIS deployments is configured at the Supervisor level under Workload Management &gt; Supervisors &gt; Configure &gt; Identity Providers. When a PAIS region is created for a Supervisor, an identity provider entry is automatically created in VMware vCenter for that Supervisor, linking the Supervisor namespace to the configured OIDC source.
-The Model Gallery, the curated repository for ML models in PAIS, restricts access to model artifacts and the training data used to tune them through Harbor project access controls. These controls scope which users and service accounts can read, push, or manage sensitive model data, adding an IAM enforcement layer to the model supply chain. A Harbor registry is recommended for PAIS deployments, and OCI-compliant registries from other vendors are also supported.
-PAIS Knowledge Bases extend IAM to ingested data sources. Confluence data sources authenticate with a user name and password or a personal access token, while Microsoft SharePoint On-Premises data sources authenticate with a user name and password. Personal access tokens for Knowledge Bases are generated from user account settings and used for programmatic access to linked data sources.
-PAIS integrates with Grafana for metrics visualization using the same OIDC provider, extending the IAM model to the observability layer so that operators authenticate through the configured identity provider before accessing PAIS dashboards.</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to identity and access management by providing identity-aware network enforcement through Identity Firewall, which integrates with Active Directory to apply firewall policy based on authenticated user identity rather than IP address alone. Identity Firewall supports assigning Active Directory users and groups as source criteria in both distributed firewall rules and gateway firewall rules, applying to tier-0 and tier-1 gateways. This allows organizations to enforce network access policy by user or group membership rather than relying solely on IP-based controls.
-Within its management plane, the Security Services Platform implements role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. These roles govern access to security policy management, analytics, incident response, and diagnostic functions across the platform. Network Detection and Response enforces the same five-role RBAC model for triage operations such as viewing detections and campaigns, and for configuration operations including SIEM integration management. For authentication, the Security Services Platform supports Active Directory and OpenLDAP as external identity sources, with one identity source configurable at a time. The License Hub integrates with external identity providers to store and manage user and group information for access delegation.
-Centralized IAM for organizational users, including VCF SSO, MFA, and directory lifecycle management, is handled by VCF and falls outside vDefend's scope.</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
 Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
@@ -1272,118 +1173,12 @@
 The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
         </is>
       </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) incorporates multiple identification and access management mechanisms that support organization-wide IAM controls within the data services layer.
-DSM implements role-based access control with two defined roles: the DSM Admin role, which can create, monitor, and manage all data services in the environment, and the DSM User role, which is restricted to managing and monitoring data services within the namespaces to which the user has been granted access. These roles are assigned at user creation time and govern what each user can see and do within the DSM interface. The Permissions view in the DSM dashboard provides administrators with a centralized location for creating, monitoring, and managing all configured users.
-DSM supports two identity sources, which can be used independently or together. Local users are created directly within DSM, with credentials validated by matching email address and password. LDAPS users are sourced from a configured LDAP identity provider, allowing organizations to extend their existing directory service into DSM. When LDAPS is configured, administrators can import users from the directory provider and assign them DSM Admin or DSM User roles. DSM also supports group-based access control: Directory Service Groups from the LDAP provider can be assigned roles directly, so group membership in the external directory determines access level in DSM without requiring per-user assignments.
-At the database level, DSM extends authentication controls beyond the platform management layer. MySQL database instances support LDAPS authentication using Active Directory. PostgreSQL and other database instances support host-based authentication (HBA) rule configuration, which determines which clients are permitted to authenticate to a given database instance. SQL Server instances support Windows Authentication through Active Directory integration, enabling Kerberos-based authentication so that clients such as SQL Server Management Studio running on domain-joined machines can authenticate via single sign-on. SQL Server also uses contained database users, where identity information resides within the database itself rather than at the server level. Administrators can configure SQL Server instances with either a SQL User or Windows Principal as the primary administrator identity, with Windows Principal available for Active Directory-integrated clusters. An internal dsm_mgmt management login restricts users from accessing or modifying system-level objects, keeping administrative operations within an isolated context.
-Namespace isolation adds a further access boundary. DSM namespaces enforce role-based access control that allows multiple users to work jointly on data services within a namespace while remaining isolated from data services in other namespaces. This supports least-privilege access within multi-tenant deployments.</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) provides a dedicated administrative identity and access management plane through the Avi Controller, supporting multiple authentication methods and fine-grained authorization controls that allow organizations to implement IAM policies across both the management plane and the application delivery layer.
-For administrative access, the Avi Controller supports local user accounts, LDAP and LDAPS directory integration, SAML-based federated authentication (including integration with Workspace ONE Access for catalog-based application access), basic authentication, and OAuth/OIDC for API access. Auth Mapping Profiles allow organizations to map external directory groups to specific roles and tenants, so that group membership in an external identity provider directly controls what a user can access within Avi.
-Authorization is handled through role-based access control (RBAC) with object-level granularity. Avi's extended granular RBAC uses markers, which are labels assigned to objects, to enable fine-grained authorization based on object ownership and classification. Permission categories cover Operations (including alerts, actions, and traffic capture) and Administration (including controller, tenant, user, role, and system configuration management). This allows restrictions so that a user's permissions apply only to the specific resources matching the markers assigned to their role. RBAC covers object categories including Virtual Services, Application Profiles, SSL/TLS Certificates, Certificate Management Profiles, Cloud definitions, TCP/UDP Profiles, Persistence Profiles, Health Monitors, Analytics Profiles, IP Address Groups, String Groups, SSL/TLS Profiles, PKI Profiles, and Authentication Profiles, with distinct read and write access levels configured per object type.
-For multi-tenant deployments, Auth Mapping Profiles support tenant isolation with configurable user group to role mappings, allowing organizations to enforce separation between teams or business units operating within the same Avi Controller.
-The Avi License Hub supports role-based access control through an external identity provider, with three predefined roles: Enterprise Admin (full access for all operations, including upgrades and authentication configuration), Auditor (view-only access for tracking activity without making changes), and Support Bundle Collector (restricted to collecting system logs and diagnostics). Management interface access is further controlled through restrictions on allowed ciphers and HMACs for management sessions.
-For deployments involving the Avi Kubernetes Operator (AKO), Kubernetes RBAC policies can be applied to AKO Custom Resource Definitions (CRDs) to enforce stricter access control over routing configuration for specific user groups. The Avi Controller also implements RBAC at the Kubernetes and OpenShift cluster level by assigning tenants and roles to user accounts.
-At the application layer, Avi can enforce client authentication using OAuth, SAML, JWT token validation, and mutual TLS with client certificates, extending access control to the traffic flowing through virtual services rather than only to the management interface.
-Organizations are responsible for defining roles, mapping directory groups to permissions, establishing naming conventions for markers, and maintaining user lifecycle processes. Avi provides the technical mechanisms; the governance and operational processes for identity management must be organized by the teams managing the deployment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Tenet 7</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>AST-02.6, AST-02.8, AST-02.9, DCH-24.1, GOV-05, MON-01, MON-01.2, MON-01.4, MON-02, MON-02.1, MON-02.2, MON-02.3, NET-14.7, THR-01, THR-03</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>The enterprise collects as much information as possible about the current state of assets, network infrastructure and communications and uses it to improve its security posture. An enterprise should collect data about asset security posture, network traffic and access requests, process that data, and use any insight gained to improve policy creation and enforcement. This data can also be used to provide context for access requests from subjects (see Section 3.3.1).</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides enterprise-wide monitoring through integrated tools that span infrastructure health, performance metrics, compliance assessment, log analysis, and alerting.
-VCF Operations continuously monitors the operational state of all VCF components to detect conditions that may affect availability or compliance. It collects metrics across compute, storage, and networking resources, and correlates them over time to identify trends that may lead to potential failures. VCF Health, a component of VCF Operations, continuously monitors the operational state of VCF components to verify they are functioning as expected, giving platform operators a single view of operational status. Platform operators can configure alerts, perform log analysis, run infrastructure diagnostics, and review VCF health from a unified interface.
-VCF Operations provides continuous compliance management by monitoring infrastructure against industry-standard benchmarks and custom policies. Administrators can create custom compliance benchmarks that monitor selected alert definitions and policies, tailoring the monitoring posture to organizational requirements. The platform assesses objects based on selected compliance policies and activates alert definitions associated with the current scorecard, providing ongoing visibility into compliance status. Compliance-related alerts are triggered on objects and displayed through a dedicated compliance alert subtype.
-The alerting subsystem in VCF Operations supports the full lifecycle of alert management. Administrators can configure and manage alert definitions to monitor infrastructure events and conditions, including performance metrics, log events, and custom conditions configured through the Management Pack Builder. The Platform Health Alerts page provides a centralized view of all alerts related to overall system health, including alerts from data sources and infrastructure nodes. Health alerts are generated for conditions that affect the health of the environment and require immediate attention. Administrators can create policies to govern how alert definitions are evaluated, including which objects to monitor and what thresholds to apply, and can apply consistent practices to optimize alert behavior across monitored objects.
-VCF Operations supports flexible grouping and scheduling to align monitoring with operational realities. Custom groups can be configured with automatic membership criteria to support monitoring strategies and achieve a high level of automation. Maintenance schedules can be assigned to objects undergoing planned downtime to keep monitoring data accurate and avoid false alerts when an object is offline for scheduled maintenance.
-VCF Log Management provides centralized log collection and analysis. It ingests logs from VMware vCenter, VMware ESX hosts, NSX, vSAN, VCF Automation, VCF Operations, VCF Identity Broker, VCF Operations for Networks, and VCF Operations HCX. VCF Operations and VCF Log Management must be integrated to implement the centralized log collection architecture. The platform provides dashboards and analytics for troubleshooting and security investigation. Log-based alert definitions allow administrators to trigger notifications when specific log patterns appear across monitored systems. Log forwarding to external SIEM or syslog targets is configurable, with support for TLS encryption to protect log data in transit. The vCenter syslog forwarding API supports TCP, UDP, TLS, and RELP protocols. NSX Manager syslog supports TLS and requires port 6514 for encrypted log transmission.
-At the vSphere layer, the alarm infrastructure integrates with events and performance counters to provide real-time alerting. The MetricAlarmExpression data object allows administrators to set alarms on specific performance metrics with configurable monitoring intervals and aggregation functions for processing data points. The vSphere Client provides direct visibility into tasks and events for change tracking and troubleshooting. VCF ships with preconfigured vSphere alarms that are active by default and monitor specific components including the Identity Management Service, Message Bus Configuration Service, ESX Agent Manager, VMware Service Control Agent, vSphere HA host status, and host connection and power state. The vCenter Management Interface provides appliance-level health visibility through an Overall Health badge that reflects one of five states (Good, Warning, Alert, Critical, or Unknown) across all vCenter components, and notifies administrators of available security patches through Critical or Alert badge indicators when automatic patch checks are enabled.
-When VCF Automation is integrated with VCF Operations, the Insights dashboard and Alerts tab provide real-time capacity awareness and alert information for VCF Automation objects, giving IT teams visibility into resource usage across both provisioned workloads and the underlying infrastructure. The VCF Automation Monitor tab surfaces deployment health information sourced from VCF Operations, and deployment cards display Last Request Status information that tracks the most recent operation on each deployment (Create, Update, or Delete) and its outcome (Successful, In Progress, or Failed). The Management Pack Builder allows administrators to set up event definitions for integrated systems, monitoring specific conditions or thresholds and configuring alerts for proactive management. Management Packs extend monitoring to network devices, including sensor monitoring for devices such as switches and routers. Adapters can be installed on VCF Operations nodes to extend monitoring to additional systems and data sources beyond the core VCF components.
-The VMware Kubernetes Service (VKS) layer of VCF extends enterprise monitoring to container workloads and Kubernetes infrastructure. VKS clusters support MachineHealthCheck objects for both control plane nodes and worker node deployments; administrators manage these through the VCF CLI vcf cluster machinehealthcheck command, which supports configuration of unhealthy-condition definitions, maximum unhealthy thresholds (expressed as an absolute number or a percentage), and label selectors to target specific machines. The VCF CLI vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands retrieve node and control plane health status on demand. VKS cluster health conditions, including the Ready and ControlPlaneReady status indicators, reflect the operational state of each cluster and are accessible via kubectl and the VCF CLI. The VCF Automation Provider Management UI includes a Services overview interface that exposes VKS cluster management functions and the health status of all cluster elements, giving platform operators a centralized view of the VKS tier. The Kubernetes API server within VKS clusters exposes diagnostic and health check endpoints (/healthz, /livez, /readyz, /statusz, and /metrics) that external monitoring systems can scrape to track API server availability and readiness; the kube-apiserver also emits the kubernetes_healthchecks_total counter and kubernetes_healthcheck gauge metric, which report structured health check status for components including etcd and autoregister-completion. Access to these monitoring endpoints is governed by the built-in Kubernetes system:monitoring RBAC group, which grants read access to liveness, readiness, and metrics endpoints while restricting broader cluster access. The Kubernetes Watch API allows monitoring tools to track changes to any API object as a live stream, supporting event-driven monitoring without continuous polling. The Node Problem Detector monitors node health and surfaces node-level problems as Kubernetes events and node conditions that external monitoring systems can consume via the event stream.
-For workload-level monitoring within VKS clusters, Prometheus Operator is available as a standard package and defines custom resource definitions to deploy and manage Prometheus and Alertmanager StatefulSets, enabling high-availability alerting configurations. The Prometheus Alertmanager custom resource definition configures alert grouping, inhibition, and routing to external notification systems. The Istio service mesh, also available as a standard package on VKS clusters, provides service-level monitoring alongside its traffic management capabilities. The Dynatrace Operator can be deployed on VKS clusters to automate the deployment, scaling, and maintenance of the Dynatrace monitoring stack. Historical analysis, dashboarding, and alerting on cluster-level metrics require a dedicated monitoring solution configured to scrape the VKS metrics endpoints and subscribe to the Kubernetes event stream. The vcf cluster support-bundler create command gathers diagnostic information from Supervisor and VKS clusters when troubleshooting is needed.
-At the network layer, NSX provides monitored indicators including node uptime status, deployment status, management and controller connections, tunnel status, PNIC status, and uptime duration. NSX time series APIs allow viewing data such as VPN statistics, including metadata about the number of tunnels configured and how many are up or down at a given time.
-VCF Operations also supports self-monitoring through the VCF Operations adapter, which collects internal metrics such as activity success counts. This allows administrators to verify that the monitoring platform itself is functioning correctly. The VCF Operations policy engine monitors conditions and generates events to react to changing states in the orchestrator server or connected technologies. The Adapter Instance monitoring interval is configurable, with intervals as granular as five minutes.
-VMware Private AI Services (PAIS) includes a built-in observability stack that supplies monitoring data for AI infrastructure and AI workloads. PAIS Controller metrics are exposed at a Prometheus metrics endpoint on the pais-controller-manager service, allowing collection by monitoring systems and visualization in observability platforms such as Grafana. Observability is activated by updating the PAISConfiguration custom resource with optional sections for Prometheus metrics collection and LLM trace forwarding. The Prometheus runtime can be configured with a specified storage class policy and a configurable metrics retention period, giving administrators control over how long monitoring data is stored. A Prometheus server pod must be in a ready and running state for observability to function.
-LLM trace data from PAIS can be forwarded to an OpenTelemetry Collector endpoint over http/protobuf or gRPC, providing distributed tracing for AI model inference activity. The observability.llmTraces configuration governs trace forwarding and works alongside the Prometheus metrics pipeline to produce two signals: metrics for health and performance, and traces for inference-level behavior. PAIS Controller metrics include the Model Endpoint Controller and PAIS Configuration Controller, giving monitoring platforms component-level visibility into PAIS operations.
-In 9.1, PAIS adds direct integration with VCF Operations. The controller-pod-metrics-streaming setting activates streaming of PAIS controller pod metrics from the Supervisor cluster to VCF Operations, allowing administrators to view PAIS metrics alongside other VCF infrastructure metrics. A Telegraf deployment in the vmware-system-monitoring namespace uses a telegraf-user-config ConfigMap to manage user-configured monitoring endpoints for PAIS. The VCF Consumption CLI connects to the Supervisor endpoint and enables VI administrators to stream metrics from the PAIS controller pod. DevOps engineers can visualize health and performance metrics for PAIS components running in a VCF Automation namespace using Grafana, and MLOps engineers and application developers can monitor the health, quality, and behavior of AI applications and the models used in agents through the same observability platforms.
-PAIS supplies the technical monitoring mechanisms this control requires. Enterprise-wide orchestration of monitoring controls, including alert threshold definition, escalation procedures, and integration with a centralized monitoring or log management platform, remain organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (vDefend) supports network security monitoring through multiple integrated capabilities that contribute to enterprise-wide monitoring frameworks.
-Security Intelligence, hosted on the Security Services Platform (SSP), provides continuous visibility into network traffic flows across protected workloads. It monitors flows between application pairs, updates the Policy Protection Status for each application to indicate that flows are being monitored, and continuously detects new flows between environment pairs, alerting administrators to unauthorized or unexpected traffic. The Monitor &amp; Plan Overview page presents a consolidated view of pending actions, data collection activity status, network security posture, flow trends, and a summary of suspicious traffic. The Security Intelligence Recommendations monitoring capability checks for changes in the scope of monitored entities every hour when the Monitoring toggle is enabled, allowing administrators to keep policy recommendations current as environments evolve. Segmentation Monitoring provides dedicated views of application and infrastructure flows with configurable time ranges spanning from the last hour to the last month, and displays flows related to detected infrastructure servers in a specified time interval.
-The Network Detection and Response (NDR) Sensor checks the status of activated detection features every 15 minutes and updates its configuration accordingly, supporting sustained threat detection coverage. NDR Sensor health status monitoring tracks whether key components, including network traffic capture, file analysis, and data transmission, are operating properly. The NDR Sensor also sends alerts notifying administrators of conditions such as services being down, high CPU, memory, or disk usage, packet drops, or missed heartbeats. NDR provides role-based access control covering triage operations such as viewing detections and campaigns, as well as SIEM configuration management.
-The Security Services Platform monitors its own health, with Yellow or Red health status indicators displayed when issues occur in subcomponents. SSP monitoring tracks the status of the flow clustering job that runs every hour and reports suspicious traffic detector execution status after each run, with values such as SUCCESS, NOT_ENOUGH_BASELINE, and FAILURE.
-The Security dashboard provides a consolidated view for monitoring and configuring security features across network workloads. In federated deployments, the Global Manager provides centralized event management and monitoring for malicious IP blocking activity across all Local Managers.
-vDefend generates Unified Security Logs that VCF Log Management can collect and analyze. These logs cover Distributed Firewall, Gateway Firewall, Identity Firewall, FQDN Analysis, TLS Inspection, Intrusion Detection/Prevention System (IDPS), and URL Filtering activity. Broader log aggregation and SIEM correlation for enterprise-wide monitoring remain the responsibility of the SIEM and logging infrastructure deployed alongside vDefend.</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
-Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
-PNR includes a health monitoring service that checks each health finding every five minutes and records a timestamp at each check. Health findings are tracked with status history that can be reviewed over configurable time periods, defaulting to a 24-hour window. The Protection and Recovery Appliance supports syslog forwarding to a remote syslog server for log analysis and centralized monitoring, allowing appliance-level events to flow into existing log management infrastructure.
-The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
 DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
@@ -1395,6 +1190,199 @@
 Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
         </is>
       </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer contributes to Zero Trust Architecture by enforcing authentication and authorization at the application delivery layer before client requests reach protected workloads. Avi's SSO Policy, configured per virtual service, supports Authentication Rules and Authorization Rules that validate JSON Web Tokens, OAuth 2.0 access tokens, and OIDC claims on every incoming request. Clients that present invalid or absent credentials are denied access before any request is forwarded to the backend resource. This per-virtual-service enforcement model means each application can independently require successful authentication as a condition of access.
+Auth Mapping Profiles extend this authentication model into the Avi Controller's administrative plane. These profiles map authenticated user identities, including identities sourced from LDAP, SAML, or other external directory services, to specific tenants and roles with varying permission levels. Auth Mapping rules can be configured to deny all privileges to specific users, blocking them from obtaining any role or tenant assignment on login. When remote authentication is configured, administrators can independently enable or disable local user login, supporting stricter authentication policy enforcement. A user without a matching rule in the Auth Mapping Profile receives no privileges on login. Auth Mapping Profiles should be configured to enforce tenant isolation except for designated super users who require cross-tenant access.
+At the management plane, administrators can restrict the source IP address ranges permitted to reach the Avi Controller and enforce strong password requirements. User Account Lockout is implemented on the Controller as a mechanism that blocks access after repeated failed authentication attempts. User accounts can be scoped to specific tenants and granted different roles within each tenant, limiting the blast radius of a compromised credential. HTTP security policies attached to virtual services are configurable to meet the security requirements applicable to each deployed application.
+In VCF-integrated deployments, the Avi PKI Profile contains the list of Trusted Authorities allowed to sign client certificates and can be used to implement Zero Trust security between the server and the client. This certificate-based mechanism supports mutual authentication at the application delivery tier, complementing token-based authentication for workloads that rely on client certificate validation rather than OAuth or OIDC flows.
+Full Zero Trust Architecture across a VCF environment requires capabilities beyond what Avi provides at the application delivery tier. Network-layer microsegmentation between workloads is provided by VMware vDefend, which is a separate product. OAuth, OIDC, and SAML federation require an external identity provider. The organizational policies that govern how authentication is enforced for all users and all devices must be defined and maintained by the organization; Avi provides the enforcement point for application traffic but does not itself constitute a complete ZTA implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Tenet 6</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>AST-02.2, AST-02.5, AST-02.9, IAC-01, IAC-01.2, IAC-06, MON-01, NET-01.1</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>All resource authentication and authorization are dynamic and strictly enforced before access is allowed. This is a constant cycle of obtaining access, scanning and assessing threats, adapting, and continually reevaluating trust in ongoing communication. An enterprise implementing a ZTA would be expected to have Identity, Credential, and Access Management (ICAM) and asset management systems in place. This includes the use of multifactor authentication (MFA) for access to some or all enterprise resources. Continual monitoring with possible reauthentication and reauthorization occurs throughout user transactions, as defined and enforced by policy (e.g., time-based, new resource requested, resource modification, anomalous subject activity detected) that strives to achieve a balance of security, availability, usability, and cost-efficiency.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides built-in Authenticate, Authorize, and Audit (AAA) capabilities across its component stack, giving organizations a strong technical foundation for governing AAA within the platform.
+For authentication, VCF SSO is the centralized identity broker. VMware vCenter can be federated with an external enterprise identity provider, which handles authentication in a federated model and enables flexible options such as multifactor authentication, automatic user registration, and termination of users across services. Named external identity providers supported for vCenter federation include Okta, with provider-specific configuration procedures available for each. NSX Manager supports local authentication, LDAP authentication, and OIDC authentication with configurable identity provider selection. VCF Automation allows organizations to define a shared identity provider and authenticate users through configurable authentication mechanisms, including redirections to external identity providers. The Identity API in VCF Automation provides programmatic management of authentication and authorization providers. The vCenter Client Credentials grant type also allows application-to-identity-provider authentication without a human user present, supporting machine-to-machine authentication scenarios. VMware ESX and vCenter validate user credentials against configured identity stores.
+At the Kubernetes consumption layer, VMware Kubernetes Service (VKS) clusters support two authentication methods: VCF SSO and OIDC-compliant external identity providers. Administrators register an external provider by configuring the identity provider issuer URL, client credentials, and certificate authority through the Supervisor, enabling providers such as Okta. DevOps users then authenticate to the cluster using their identity provider credentials, keeping cluster authentication federated to a centrally managed identity store rather than relying on cluster-local accounts. Kubernetes hardening guidance recommends external authentication sources such as OIDC for production clusters with multiple users accessing the Kubernetes API directly. OIDC authentication is distributed to developer workstations through kubeconfig files, and custom ClusterClass configurations can be used to authenticate developers using existing corporate identity systems. Argo CD, when deployed as a Supervisor Service, supports PKCE-enabled OIDC authentication through the enablePKCEAuthentication field in the spec.oidc configuration, extending federated identity management to continuous delivery workflows. Infrastructure credentials, including service account tokens, can be configured to use short-lived certificates with automated rotation.
+For authorization, VCF implements a permissions-based model across its components. Authenticated users on VMware ESX and vCenter can view objects or invoke operations depending on the permissions associated with their account. The vCenter authorization model provides consistent security control regardless of how users connect to the environment. NSX authentication best practices include defining access controls based on user roles and permissions and integrating with identity providers.
+At the Kubernetes layer, the Supervisor exposes the full Kubernetes RBAC model through Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings, which control what authenticated principals can do within a cluster or namespace. The Node authorizer supports TokenReviews and SubjectAccessReviews for delegated authentication and authorization checks. IAM role trust policies can be scoped to specific service accounts and namespaces to enforce least privilege across workloads. Kubernetes service accounts provide identity for Pods, allowing security software to group Pods into distinct security contexts. The Secret Store Supervisor Service enforces role-based access control for administrators, DevOps engineers, and application tenants managing and distributing sensitive data. Harbor Registry, deployable as a standard package on VKS clusters, secures container artifacts with policies and role-based access control, and its administrative interface allows administrators to verify authentication and access control configurations.
+Audit capabilities are built into the platform at multiple levels. All API calls to NSX Manager are subject to authentication and authorization and generate audit logs. NSX supports audit data generation as a security functional requirement. NSX Manager and NSX Edge both include a dedicated audit role with separate credentials. The NSX Manager audit user has read-only privileges to the NSX environment and is not active by default; it must be explicitly activated after installation by an admin through the CLI. This separation of the audit role from administrative roles supports segregation of duties for audit functions. Within VCF SSO, NSX-related audit access is controlled through the NsxAuditors group, alongside NsxAdministrators and NsxViAdministrators, providing structured group-based assignments for NSX roles within the identity provider. NSX Manager exposes API endpoints (/api/v1/node/aaa/auth-policy and related paths) that return authentication policy settings, allowing administrators to validate authentication configuration across nodes programmatically. VCF Operations generates audit events across categories including access, access control, account management, configuration, data access, network, notification, permissions, session, system, policy, and firewall actions. These audit events are accessible through the Security menu and can be filtered, searched, and reviewed in detail.
+The Kubernetes API server includes built-in audit logging. Audit events include an authenticationMetadata object that records how each request was authenticated, and when a request uses constrained impersonation the event includes an impersonationConstraint field that records which constrained impersonation verb authorized the request. Audit annotations capture authorization.k8s.io/decision and authorization.k8s.io/reason, recording authorization outcomes and their justifications in the audit log. ValidatingAdmissionPolicy objects emit audit annotations constructed from the policy name and a qualified key, with the annotation key included in the audit event, giving administrators a policy-level audit trail for admission control decisions. Separating service account creation from human user onboarding makes it easier to maintain distinct audit strategies for workloads and individuals.
+Organizations looking to govern AAA within VCF should configure identity provider federation for vCenter and NSX Manager to centralize authentication through their enterprise identity provider. At the Kubernetes layer, configuring OIDC on VKS clusters and registering the same enterprise identity provider keeps workload cluster authentication aligned with the platform's identity governance. Enabling the NSX audit user and configuring audit logging across all components, including the Kubernetes API server, provides the audit leg of the AAA triad. The platform's support for multiple authentication methods (local, LDAP, OIDC) and its role-based authorization model give administrators the technical controls needed to enforce AAA policies. However, the governance policies themselves, including which AAA solutions to use, how to review and approve AAA configurations, and how to handle AAA for external service providers, must be established and maintained as organizational processes outside the platform.
+VMware Private AI Services (PAIS) provides authentication and authorization mechanisms for its AI-specific services that organizations integrate into a broader AAA governance framework.
+PAIS authentication uses OIDC. During service activation, an administrator configures the OIDC issuer URL, the client ID (pais-authentication-id), and the required scopes (openid, groups, offline_access). The configuration also accepts the OIDC issuer certificate and supports an Extra Audiences setting that allows PAIS to accept access tokens minted for additional OAuth 2.0 clients when the OIDC provider requires it. PAIS requires HTTPS-based communication for the OIDC integration, and activation must be coordinated with the OIDC provider administrator to establish the identity and access management relationship.
+Access to PAIS is governed by the authorizedGroups setting, which restricts service access to user accounts that are members of specified OIDC groups (for example group-for-pais-access-01). Group-based authorization routes identity decisions made in the OIDC provider directly into PAIS access control without separate per-service user provisioning.
+PAIS supports CA trust bundle management to establish certificate-validated communication with the OIDC provider, Harbor registries, content management systems, and external knowledge base sources. The Grafana observability integration uses OIDC for metrics visualization access and should enable PKCE and refresh tokens for its own authentication flow. Harbor registry access uses credential-based authentication via oras login for artifact push and model pull operations, and PAIS is compatible with OCI-compliant registries from other vendors. Knowledge Bases that ingest from Confluence authenticate using either a username and password or a personal access token. Remote MCP servers connected to PAIS can optionally use static authentication tokens. Air-gapped deployments require the self-hosted registry location and login credentials when the registry requires authentication.
+Identity and access management for PAIS must be configured in coordination with an external OIDC provider administrator. PAIS provides the integration hooks and access enforcement mechanisms; the OIDC provider itself, including group lifecycle management and policy enforcement, is operated and governed separately by the organization.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to identity and access management by providing identity-aware network enforcement through Identity Firewall, which integrates with Active Directory to apply firewall policy based on authenticated user identity rather than IP address alone. Identity Firewall supports assigning Active Directory users and groups as source criteria in both distributed firewall rules and gateway firewall rules, applying to tier-0 and tier-1 gateways. This allows organizations to enforce network access policy by user or group membership rather than relying solely on IP-based controls.
+Within its management plane, the Security Services Platform implements role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. These roles govern access to security policy management, analytics, incident response, and diagnostic functions across the platform. Network Detection and Response enforces the same five-role RBAC model for triage operations such as viewing detections and campaigns, and for configuration operations including SIEM integration management. For authentication, the Security Services Platform supports Active Directory and OpenLDAP as external identity sources, with one identity source configurable at a time. The License Hub integrates with external identity providers to store and manage user and group information for access delegation.
+Centralized IAM for organizational users, including VCF SSO, MFA, and directory lifecycle management, is handled by VCF and falls outside vDefend's scope.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) implements authenticate, authorize, and audit (AAA) mechanisms for replication and recovery operations. Authentication uses VCF SSO. The PNR server acquires a holder-of-key SAML token from VCF SSO and presents it in a cryptographically signed envelope when establishing authenticated communication channels to remote services such as VMware vCenter. PNR uses service account authentication for server-to-vCenter communication, and a domain-level service account created by vCenter is used when PNR runs in an Enhanced Linked Mode environment. When connecting peer vCenter instances that reside in different or the same SSO domains, PNR also supports credential-based authentication. The PNR Appliance Management Interface requires authentication as the admin user for service management, network configuration, time zone settings, storage replication adapter configuration, and site unregistration workflows. The default admin password is set during initial deployment and is expected to be changed by the operator. PNR exposes Authentication APIs as part of its REST API gateway, including a REST endpoint to log out an authenticated session.
+Authorization is enforced through PNR's privileges, roles, and permissions model. PNR performs operations using the user credentials supplied when the protected and recovery sites are connected, and permission checks apply at both sites for cross-site operations. The configuration import and export tool accepts the --localAuthUseSA and --remoteAuthUseSA parameters, which select whether a Service Account file is used for authentication to the local or remote site. PNR and later supports Service Account authentication for importing or exporting configuration data.
+Audit logging records replication and recovery operations and security-relevant events. PNR records operational information in log files that do not contain private keys or passwords. Authorization errors and certificate verification errors are written with timestamps and component information to security-related log files for audit trail purposes. Replication lifecycle events generate audit log entries, for example the AutoprotectEnabledRpEvent entry that indicates Automatic Protection has been activated for a replication provider.</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) incorporates multiple identification and access management mechanisms that support organization-wide IAM controls within the data services layer.
+DSM implements role-based access control with two defined roles: the DSM Admin role, which can create, monitor, and manage all data services in the environment, and the DSM User role, which is restricted to managing and monitoring data services within the namespaces to which the user has been granted access. These roles are assigned at user creation time and govern what each user can see and do within the DSM interface. The Permissions view in the DSM dashboard provides administrators with a centralized location for creating, monitoring, and managing all configured users.
+DSM supports two identity sources, which can be used independently or together. Local users are created directly within DSM, with credentials validated by matching email address and password. LDAPS users are sourced from a configured LDAP identity provider, allowing organizations to extend their existing directory service into DSM. When LDAPS is configured, administrators can import users from the directory provider and assign them DSM Admin or DSM User roles. DSM also supports group-based access control: Directory Service Groups from the LDAP provider can be assigned roles directly, so group membership in the external directory determines access level in DSM without requiring per-user assignments.
+At the database level, DSM extends authentication controls beyond the platform management layer. MySQL database instances support LDAPS authentication using Active Directory. PostgreSQL and other database instances support host-based authentication (HBA) rule configuration, which determines which clients are permitted to authenticate to a given database instance. SQL Server instances support Windows Authentication through Active Directory integration, enabling Kerberos-based authentication so that clients such as SQL Server Management Studio running on domain-joined machines can authenticate via single sign-on. SQL Server also uses contained database users, where identity information resides within the database itself rather than at the server level. Administrators can configure SQL Server instances with either a SQL User or Windows Principal as the primary administrator identity, with Windows Principal available for Active Directory-integrated clusters. An internal dsm_mgmt management login restricts users from accessing or modifying system-level objects, keeping administrative operations within an isolated context.
+Namespace isolation adds a further access boundary. DSM namespaces enforce role-based access control that allows multiple users to work jointly on data services within a namespace while remaining isolated from data services in other namespaces. This supports least-privilege access within multi-tenant deployments.</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer contributes to Zero Trust Architecture by enforcing authentication and authorization at the application delivery layer before client requests reach protected workloads. Avi's SSO Policy, configured per virtual service, supports Authentication Rules and Authorization Rules that validate JSON Web Tokens, OAuth 2.0 access tokens, and OIDC claims on every incoming request. Clients that present invalid or absent credentials are denied access before any request is forwarded to the backend resource. This per-virtual-service enforcement model means each application can independently require successful authentication as a condition of access.
+Auth Mapping Profiles extend this authentication model into the Avi Controller's administrative plane. These profiles map authenticated user identities, including identities sourced from LDAP, SAML, or other external directory services, to specific tenants and roles with varying permission levels. Auth Mapping rules can be configured to deny all privileges to specific users, blocking them from obtaining any role or tenant assignment on login. When remote authentication is configured, administrators can independently enable or disable local user login, supporting stricter authentication policy enforcement. A user without a matching rule in the Auth Mapping Profile receives no privileges on login. Auth Mapping Profiles should be configured to enforce tenant isolation except for designated super users who require cross-tenant access.
+At the management plane, administrators can restrict the source IP address ranges permitted to reach the Avi Controller and enforce strong password requirements. User Account Lockout is implemented on the Controller as a mechanism that blocks access after repeated failed authentication attempts. User accounts can be scoped to specific tenants and granted different roles within each tenant, limiting the blast radius of a compromised credential. HTTP security policies attached to virtual services are configurable to meet the security requirements applicable to each deployed application.
+In VCF-integrated deployments, the Avi PKI Profile contains the list of Trusted Authorities allowed to sign client certificates and can be used to implement Zero Trust security between the server and the client. This certificate-based mechanism supports mutual authentication at the application delivery tier, complementing token-based authentication for workloads that rely on client certificate validation rather than OAuth or OIDC flows.
+Full Zero Trust Architecture across a VCF environment requires capabilities beyond what Avi provides at the application delivery tier. Network-layer microsegmentation between workloads is provided by VMware vDefend, which is a separate product. OAuth, OIDC, and SAML federation require an external identity provider. The organizational policies that govern how authentication is enforced for all users and all devices must be defined and maintained by the organization; Avi provides the enforcement point for application traffic but does not itself constitute a complete ZTA implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Tenet 7</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>AST-02.6, AST-02.8, AST-02.9, DCH-24.1, GOV-05, MON-01, MON-01.2, MON-01.4, MON-02, MON-02.1, MON-02.2, MON-02.3, NET-14.7, THR-01, THR-03</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>The enterprise collects as much information as possible about the current state of assets, network infrastructure and communications and uses it to improve its security posture. An enterprise should collect data about asset security posture, network traffic and access requests, process that data, and use any insight gained to improve policy creation and enforcement. This data can also be used to provide context for access requests from subjects (see Section 3.3.1).</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides automated mechanisms to integrate audit record analysis with vulnerability scanning data, network performance monitoring, system monitoring, and other operational sources across the infrastructure stack. This integration is achieved through several interconnected components. VCF Operations is the centralized monitoring and analytics platform, and VCF Log Management aggregates log data from multiple VCF components into a unified collection point.
+VCF Log Management can be configured to pull tasks, events, and alerts from VMware vCenter instances and receive syslog feeds from VMware ESX hosts through its Log Collections configuration. This brings audit records from across the infrastructure into a single platform where they can be analyzed alongside operational and performance data. VCF Log Management collects and aggregates log data from vCenter and ESX hosts, providing dashboards and analytics for centralized log analysis that spans the full infrastructure stack.
+VCF Operations itself generates audit events across a broad set of categories, including Access, Access_control, Account_management, Configuration, Data_access, Network, Notification, Permissions, Session, System, Policy, and Firewall. Each audit event includes a detailed view containing information that supports analysis of events in the virtual infrastructure for suspicious user actions or system issues. The event auditing capability provides visibility into platform interaction changes across the VCF infrastructure and surfaces suspicious access events and policy violations. Audit events capture platform interactions such as user logins, logouts, capability checks, and configuration modifications.
+The audit log in VCF Operations is integrated with the syslog subsystem, and the syslog collector can be configured to collect all audit logs. This integration allows audit records to flow through the same infrastructure as system and application logs, facilitating correlation. VCF Operations can also send user activity logs to an external syslog server for security auditing, enabling correlation with third-party SIEM or security analytics platforms. System audit reports can be downloaded in PDF or XLS format for offline analysis and compliance review.
+VCF Operations provides several capabilities that support cross-source analysis and anomaly identification. Metric correlation runs on all metrics for a selected object to find metrics with similar or opposite behavioral change over the same time period, using both self-metrics and peer-object options. This allows administrators to correlate audit activity with performance deviations across the infrastructure. VCF Operations also supports dynamic thresholds for metrics, calculated based on historical and incoming data, which generate alerts when current values fall outside trended ranges. Dynamic threshold analysis uses a period of seven days of historical data before generating alerts. Alert definitions support metric event symptoms based on events from monitored systems where a selected metric violates a threshold, enabling automated responses when performance metrics indicate unusual activity.
+VCF Operations collects OS and Application Monitoring Properties for operating systems, application services, remote checks, Linux processes, and Windows services, which can be used to create reports, views, and dashboards that combine audit data with system performance and health metrics. Self-monitoring metrics track internal health indicators such as CheckThresholdAndHealth outcome observations. Sensor metrics including temperature, fan speed, and fan health state are collected for host systems, broadening the scope of monitored data available for correlation with audit records.
+At the host and network layer, ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, with configurable log levels to control the detail captured. The Syslog.global.auditRecord.remote parameter specifically enables forwarding of security audit records to the remote host defined by Syslog.global.logHost, providing a dedicated control for audit-record transmission that is separate from general syslog configuration. vCenter supports syslog forwarding to up to three remote servers using TCP, UDP, TLS, or RELP protocols, allowing audit records from across the VCF stack to be sent to a SIEM or log aggregation platform. Event streaming from vCenter to a remote syslog server can be enabled independently through the vpxd.event.syslog.enabled option, configured in the vCenter Management Interface. NSX audit logs are sent directly to the remote syslog server, and NSX logging and auditing capabilities can be integrated with logging and monitoring solutions to monitor for security events and anomalies. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission. NSX nodes can be configured to send syslog messages to multiple remote servers, each with independently specified port numbers and protocols.
+VCF Operations for Networks provides its own audit log, which is integrated with syslog so that network monitoring data can be collected alongside infrastructure logs. VCF Operations for Networks can be configured to send problem alerts and platform or collector syslogs to remote syslog servers. Audit log data from VCF Operations for Networks can also be exported in CSV format for offline analysis.
+The vCenter alarm infrastructure integrates with other server components such as events and performance counters, and supports metric-based alarm expressions that can trigger alerts when performance metrics indicate unusual activity. VCF PowerCLI supports creating metric-based alarm triggers with New-AlarmTrigger to define thresholds and conditions for CPU usage and other performance metrics. vCenter can also create alarms to monitor events on vSAN objects, including the cluster, ESX hosts, datastores, networks, and virtual machines.
+Integration with external systems extends the correlation capabilities further. In integrated environments, VCF Automation insights and alerts for monitored objects can be accessed alongside VCF Operations data through the Alerts tab in the VCF Automation main menu, providing cross-product visibility. A ServiceNow Details dashboard provides status, relationships, health, alerts, and KPIs for monitored resources, connecting infrastructure monitoring data with IT service management workflows.</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to data action mapping through its Security Intelligence and Security Services Platform (SSP) components, which provide network-level visibility into how data flows between workloads, applications, and infrastructure tiers. While creating and maintaining a formal map of where sensitive data is stored, transmitted, or processed is an organizational activity, vDefend provides the traffic analysis and asset inventory capabilities that inform such mapping efforts.
+Security Intelligence collects and visualizes network traffic flows between compute entities, displaying source and destination details for each flow including VMs, IP addresses, groups, and applications. Asset collections in Security Intelligence include groups, infrastructure assets, environments, and applications and application tiers, providing a structured view of communication patterns across the environment. The Computes View displays the types of traffic flows that have occurred between compute entities during a selected time period. The Deep Dive action shows all compute entities belonging to a group and all groups that had traffic flows with those members during the selected time period, enabling teams to trace data movement paths across the environment. Security Intelligence maintains a Workload Classification table that stores and displays compute entity classifications, which can be modified through the administrative interface. Labels can be assigned to compute entity nodes through the contextual menu in the Computes View, and the Labels panel provides an Export as CSV function that downloads a file containing compute entities assigned to labels, including object ID, name, compute type, and IP address details. Policy recommendations generated from traffic flow analysis support segmentation strategy actions with allow or drop rules.
+Security Services Platform organizes monitored assets into a hierarchy of regions, zones, environments, applications, and application tiers. The Platform Inventory view allows assets to be browsed by Regions &amp; Zones with hierarchical grouping that expands to show assigned tags with their respective scopes. The SSP Platform Inventory also collects and displays VM tags with their respective scopes for asset tracking and classification. Segmentation analysis maps inventory asset information from CSV files for publishing to NSX Manager, categorizing assets into infrastructure assets, regions and zones, environments, and applications. Security Intelligence combines this CSV-imported inventory data with infrastructure server data based on traffic flows discovered by Security Intelligence, producing a unified view available in the Summary tab. Security Intelligence discovers environments in the infrastructure after ingesting CSV file data and provides recommendations based on inter-environment traffic flows. The Segmentation Hierarchy and Infrastructure Services view displays the entire inventory assets hierarchy organized by region, zone, environment, application, and tier, with each scope listing the total number of assets included.</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
+Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
+PNR includes a health monitoring service that checks each health finding every five minutes and records a timestamp at each check. Health findings are tracked with status history that can be reviewed over configurable time periods, defaulting to a 24-hour window. The Protection and Recovery Appliance supports syslog forwarding to a remote syslog server for log analysis and centralized monitoring, allowing appliance-level events to flow into existing log management infrastructure.
+The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
+DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
+DSM's alert framework provides configurable thresholds for warning and critical conditions on key health indicators. Administrators and users can set separate warning and critical thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters. When thresholds are exceeded, DSM generates typed alerts such as Database Engine Health, Custom Config Health, and Backup Storage Health alerts. DSM monitors database replication status and raises an alert when a secondary database is not replicating data from the primary. DSM also raises an alert when metrics are no longer being received from a cluster, supporting detection of monitoring gaps. Alerts can be activated or deactivated per data service through the "Enable Alerts for DB Alert" setting, providing granular control over which databases are subject to active alerting. For each alert, DSM provides mitigation suggestions to help administrators resolve issues without disrupting database services.
+In addition to database-level alerts, DSM generates global infrastructure alerts that surface vCenter integration and infrastructure policy issues. These include INFRASTRUCTURE_POLICY_VC_ALARMS, raised when vCenter resource alarms are active; INFRASTRUCTURE_POLICY_CLUSTER_COMPLIANT and INVALID_SUPERVISOR_INFRASTRUCTURE_POLICY_STATUS, which reflect cluster compliance state; VCENTER_CONNECTIVITY, raised when vCenter connectivity fails and triggering troubleshooting steps that include verifying connectivity and checking authentication logs; and LicensingNotUpdated and vCenterBinding API status alerts that surface license and API integration conditions. A Global Alerts page in the DSM UI provides a centralized view of these alerts during and after installation and ongoing operation.
+In 9.1, DSM integrates with VCF Operations to extend observability beyond the DSM UI. When configured, VCF Operations automatically discovers and monitors PostgreSQL and MySQL clusters in the Ready state and displays a Data Services View dashboard showing active alerts and inventory items. VCF Operations presents performance data across three levels: cluster-level for overall health, node-level for infrastructure resource use, and database-level for KPIs including Active Connections, Commits, Rollbacks, and Deadlocks. This integration requires configuring the connection between DSM and VCF Operations before use.
+DSM also adds SQL Server as a supported database type, with dedicated monitoring through an integrated InfluxDB instance and Telegraf agents deployed across the provider appliance and SQL Server workload clusters. The monitoring framework supports metrics-based and status-condition-based alerts for SQL Server, covering database engine degradation, non-operational status, and automated or transaction log backup failure conditions.
+DSM supports event notification to external systems through a webhook integration. Webhooks transmit alert notifications containing the triggered date, triggered time, triggered user email, task status, previous status, and task type. This allows DSM alerts to feed into centralized monitoring or incident management platforms maintained by the organization. DSM generates plug-in registration logs that administrators can review for vCenter connectivity errors, and DSM's troubleshooting guidance directs administrators to review active vCenter infrastructure alarms and resolve underlying issues identified through the alert system.
+Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
+        </is>
+      </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
           <t>Contributes</t>
@@ -1402,12 +1390,16 @@
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
-The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
-ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
-The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
-At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
-In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
+          <t>VMware Avi Load Balancer provides multiple mechanisms for forwarding security-relevant event logs to external centralized collection systems, including SIEM platforms, syslog aggregators, and log analytics tools.
+The Avi Controller exports logs through syslog forwarding, configured via the `configure systemconfiguration` CLI command or through the Controller Settings interface. The `syslog_servers` setting specifies one or more external syslog destinations. Syslog configuration is synchronized from the Controller to Service Engines, so data-plane events from Service Engines are also forwarded to the same targets.
+For audit-focused event streaming, Avi provides Syslog-Audit-Persistence, a built-in alert action template that streams audit and security events to external syslog servers. Events forwarded in this mode are encoded in SYSLOG_RFC5425_ENHANCED format, which includes event type, object name, tenant identifier, timestamp, and the identity of the user who performed the action. Syslog transport supports both TCP (with TLS) and UDP with a configurable destination port (default 514 per RFC 5426). This covers administrative configuration changes, object-level audit events, and security alert notifications.
+The Avi Controller and Service Engines log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk, providing complete traceability of encrypted communication lifecycle events. The Avi DataScript engine supports logging of security events such as blocklisted IP access attempts using the `log()` function, making application-layer policy enforcement decisions available to the central log collector.
+Beyond the audit stream, Avi supports streaming client application logs to external syslog or logging servers for centralized monitoring and compliance audit trails. WAF Application Rule events are captured when a WAF rule fires, recording the type of attack detected and matched variable content, and these events can be forwarded to the same external collection targets. The Avi Controller also logs denial of service attack events with structured details including event ID, attack count, threshold values, and alert level.
+Avi supports integration with VCF Log Management. A VCF Log Management Log Forwarder can be configured as a syslog destination in the Avi Controller to receive events. The VCF Log Management agent, installed on an external syslog server, can parse JSON log data and forward it to the Log Forwarder. The recommended integration pattern routes logs through an intermediate proxy for JSON parsing, enabling key extraction and facilitating querying of client logs. Note that virtual service client logs should not be sent directly from the Service Engine to a Log Forwarder; the recommended path routes through an intermediate syslog server.
+The Avi Analytics Profile supports streaming of client logs to multiple external servers simultaneously, including IPv6 destinations. For assured retention of all logs, Avi documentation recommends streaming logs directly to an external server such as Splunk rather than relying on local storage. In air-gap environments, the remote syslog server must be located within the environment perimeter.
+The Avi Event Log system records all system activities, configuration changes, and operational events, including who made each change and when. Global event logs are accessible via the Operations &gt; All Events page in the Avi UI, covering all objects including deleted objects and sub-objects such as profiles and certificates. A REST API endpoint allows retrieval of event logs for a specific time period to support automated log collection workflows. Events can be filtered by type using parameters such as `event_id=CONFIG_CREATE` or `event_id=CONFIG_UPDATE` to identify configuration activity.
+Note that system component debug logs are not sent to remote syslog servers and are available only through the Tech Support generation mechanism. Similarly, virtual service logs are not pushed automatically via syslog notification; they must be pulled from an external logging system through the API or configured separately to be pushed from the Controller.
+To configure centralized log forwarding, navigate to Controller Settings and enter the target syslog server address in the Syslog configuration. For audit event streaming specifically, configure the Syslog-Audit-Persistence alert action template. For VCF Log Management integration, configure a Log Forwarder as a syslog destination in the Controller and optionally deploy the VCF Log Management agent on an intermediate syslog server for JSON parsing.</t>
         </is>
       </c>
     </row>
